--- a/data/input/In_Transit_PO data.xlsx
+++ b/data/input/In_Transit_PO data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92067E61-E66A-49E6-98EB-3B8D74A2B273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E52AD55-9B90-4DE6-82FB-A612D2B27D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED1C42A4-610F-4493-A647-7EDE7899E1B2}"/>
   </bookViews>
@@ -16,12 +16,21 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3900,7 +3909,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{AD5A3FE4-F9D3-480E-B305-3F537BEA10CA}"/>
+  <autoFilter ref="A1:P63" xr:uid="{AD5A3FE4-F9D3-480E-B305-3F537BEA10CA}"/>
   <conditionalFormatting sqref="B2:B63">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>

--- a/data/input/In_Transit_PO data.xlsx
+++ b/data/input/In_Transit_PO data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E52AD55-9B90-4DE6-82FB-A612D2B27D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3176408C-1FC3-443C-BC8D-F845195920EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED1C42A4-610F-4493-A647-7EDE7899E1B2}"/>
   </bookViews>

--- a/data/input/In_Transit_PO data.xlsx
+++ b/data/input/In_Transit_PO data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3176408C-1FC3-443C-BC8D-F845195920EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEFF41D-EF42-43B8-B072-526E55D6694D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED1C42A4-610F-4493-A647-7EDE7899E1B2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="395">
   <si>
     <t>PO Number</t>
   </si>
@@ -96,33 +96,12 @@
     <t>92099900</t>
   </si>
   <si>
-    <t>4HQYPE5P</t>
-  </si>
-  <si>
-    <t>4HQYPE5P_B0DXFPM4N2</t>
-  </si>
-  <si>
     <t>CCX1</t>
   </si>
   <si>
-    <t>B0DXFPM4N2</t>
-  </si>
-  <si>
-    <t>FBA79482</t>
-  </si>
-  <si>
-    <t>AM-S1</t>
-  </si>
-  <si>
     <t>In-Transit</t>
   </si>
   <si>
-    <t>2Z1UE8FQ</t>
-  </si>
-  <si>
-    <t>2Z1UE8FQ_B0GCP1J2HC</t>
-  </si>
-  <si>
     <t>B0GCP1J2HC</t>
   </si>
   <si>
@@ -135,24 +114,9 @@
     <t>M8</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0FQBXS6Y2</t>
-  </si>
-  <si>
-    <t>B0FQBXS6Y2</t>
-  </si>
-  <si>
-    <t>FBA79839</t>
-  </si>
-  <si>
     <t>85176290</t>
   </si>
   <si>
-    <t>AH-45 BK</t>
-  </si>
-  <si>
-    <t>2Z1UE8FQ_B0FG88HVQ8</t>
-  </si>
-  <si>
     <t>B0FG88HVQ8</t>
   </si>
   <si>
@@ -162,9 +126,6 @@
     <t>AH-50</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0DT6T6N6B</t>
-  </si>
-  <si>
     <t>B0DT6T6N6B</t>
   </si>
   <si>
@@ -177,9 +138,6 @@
     <t>AA-26</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0D3LZWTHV</t>
-  </si>
-  <si>
     <t>B0D3LZWTHV</t>
   </si>
   <si>
@@ -192,9 +150,6 @@
     <t>AM-C45</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0CQX4K9P5</t>
-  </si>
-  <si>
     <t>B0CQX4K9P5</t>
   </si>
   <si>
@@ -204,21 +159,6 @@
     <t>TD310</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0CJR76Y7G</t>
-  </si>
-  <si>
-    <t>B0CJR76Y7G</t>
-  </si>
-  <si>
-    <t>FBA79064</t>
-  </si>
-  <si>
-    <t>AA-25</t>
-  </si>
-  <si>
-    <t>2Z1UE8FQ_B0CH4VCD6R</t>
-  </si>
-  <si>
     <t>B0CH4VCD6R</t>
   </si>
   <si>
@@ -228,9 +168,6 @@
     <t>AC-6XL</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0CBCB82MT</t>
-  </si>
-  <si>
     <t>B0CBCB82MT</t>
   </si>
   <si>
@@ -240,9 +177,6 @@
     <t>AM-C39</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0CBC7QMNV</t>
-  </si>
-  <si>
     <t>B0CBC7QMNV</t>
   </si>
   <si>
@@ -252,9 +186,6 @@
     <t>AM-C11X</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0BRKFP94K</t>
-  </si>
-  <si>
     <t>B0BRKFP94K</t>
   </si>
   <si>
@@ -264,9 +195,6 @@
     <t>TD510</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0B4G94VP3</t>
-  </si>
-  <si>
     <t>B0B4G94VP3</t>
   </si>
   <si>
@@ -279,21 +207,6 @@
     <t>AA-03</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B0B4G5JG4P</t>
-  </si>
-  <si>
-    <t>B0B4G5JG4P</t>
-  </si>
-  <si>
-    <t>FBA75691</t>
-  </si>
-  <si>
-    <t>AM-W14</t>
-  </si>
-  <si>
-    <t>2Z1UE8FQ_B08NDB5NWP</t>
-  </si>
-  <si>
     <t>B08NDB5NWP</t>
   </si>
   <si>
@@ -303,9 +216,6 @@
     <t>TM20</t>
   </si>
   <si>
-    <t>2Z1UE8FQ_B01ISNU3X4</t>
-  </si>
-  <si>
     <t>B01ISNU3X4</t>
   </si>
   <si>
@@ -315,15 +225,6 @@
     <t>K1</t>
   </si>
   <si>
-    <t>2K8RKCKA</t>
-  </si>
-  <si>
-    <t>2K8RKCKA_B0GCP1J2HC</t>
-  </si>
-  <si>
-    <t>2K8RKCKA_B0CQX4K9P5</t>
-  </si>
-  <si>
     <t>27FVSNUZ</t>
   </si>
   <si>
@@ -439,6 +340,888 @@
   </si>
   <si>
     <t>Open PO</t>
+  </si>
+  <si>
+    <t>85Z5AY7C</t>
+  </si>
+  <si>
+    <t>85Z5AY7C_B0DFMNGFTD</t>
+  </si>
+  <si>
+    <t>B0DFMNGFTD</t>
+  </si>
+  <si>
+    <t>FBA79449</t>
+  </si>
+  <si>
+    <t>AM-W36</t>
+  </si>
+  <si>
+    <t>85Z5AY7C_B089FVQD3Z</t>
+  </si>
+  <si>
+    <t>B089FVQD3Z</t>
+  </si>
+  <si>
+    <t>FBA77105</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>49ZX81LQ</t>
+  </si>
+  <si>
+    <t>49ZX81LQ_B0G53PRM34</t>
+  </si>
+  <si>
+    <t>B0G53PRM34</t>
+  </si>
+  <si>
+    <t>FBA79965</t>
+  </si>
+  <si>
+    <t>AM-Mix6</t>
+  </si>
+  <si>
+    <t>49ZX81LQ_B0G53M9258</t>
+  </si>
+  <si>
+    <t>B0G53M9258</t>
+  </si>
+  <si>
+    <t>FBA79968</t>
+  </si>
+  <si>
+    <t>AI-14</t>
+  </si>
+  <si>
+    <t>49ZX81LQ_B0G53KWRWH</t>
+  </si>
+  <si>
+    <t>B0G53KWRWH</t>
+  </si>
+  <si>
+    <t>FBA79964</t>
+  </si>
+  <si>
+    <t>AM-Pro12</t>
+  </si>
+  <si>
+    <t>49ZX81LQ_B0FN7B3KWS</t>
+  </si>
+  <si>
+    <t>B0FN7B3KWS</t>
+  </si>
+  <si>
+    <t>FBA79845</t>
+  </si>
+  <si>
+    <t>UB-02</t>
+  </si>
+  <si>
+    <t>49ZX81LQ_B0B4G8ZB64</t>
+  </si>
+  <si>
+    <t>B0B4G8ZB64</t>
+  </si>
+  <si>
+    <t>FBA75675</t>
+  </si>
+  <si>
+    <t>AM-C3</t>
+  </si>
+  <si>
+    <t>49ZX81LQ_B0B4G7VWXD</t>
+  </si>
+  <si>
+    <t>B0B4G7VWXD</t>
+  </si>
+  <si>
+    <t>FBA75684</t>
+  </si>
+  <si>
+    <t>AA-04</t>
+  </si>
+  <si>
+    <t>45OUQ8YG</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0G53KWRWH</t>
+  </si>
+  <si>
+    <t>BLR8</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0FG88HVQ8</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0DT6T6N6B</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0CKHVHVQ1</t>
+  </si>
+  <si>
+    <t>B0CKHVHVQ1</t>
+  </si>
+  <si>
+    <t>FBA79005</t>
+  </si>
+  <si>
+    <t>AM-W45</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0BPLWW72Y</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0B4JRQP22</t>
+  </si>
+  <si>
+    <t>B0B4JRQP22</t>
+  </si>
+  <si>
+    <t>FBA75679</t>
+  </si>
+  <si>
+    <t>AA-02</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0B4G8ZB64</t>
+  </si>
+  <si>
+    <t>45OUQ8YG_B0B4G7VWXD</t>
+  </si>
+  <si>
+    <t>2CTKF98I</t>
+  </si>
+  <si>
+    <t>2CTKF98I_B0GN8MPYPG</t>
+  </si>
+  <si>
+    <t>B0GN8MPYPG</t>
+  </si>
+  <si>
+    <t>FBA79982</t>
+  </si>
+  <si>
+    <t>AK-61 Pro</t>
+  </si>
+  <si>
+    <t>2CTKF98I_B0GN8MFDGZ</t>
+  </si>
+  <si>
+    <t>B0GN8MFDGZ</t>
+  </si>
+  <si>
+    <t>FBA79981</t>
+  </si>
+  <si>
+    <t>AK-61 Neo</t>
+  </si>
+  <si>
+    <t>3QRG1ITC</t>
+  </si>
+  <si>
+    <t>3QRG1ITC_B0GN8RQJRG</t>
+  </si>
+  <si>
+    <t>ISK3</t>
+  </si>
+  <si>
+    <t>B0GN8RQJRG</t>
+  </si>
+  <si>
+    <t>FBA79979</t>
+  </si>
+  <si>
+    <t>AK-37-B</t>
+  </si>
+  <si>
+    <t>3QRG1ITC_B0GN8MMKY1</t>
+  </si>
+  <si>
+    <t>B0GN8MMKY1</t>
+  </si>
+  <si>
+    <t>FBA79980</t>
+  </si>
+  <si>
+    <t>AK-37-W</t>
+  </si>
+  <si>
+    <t>5AX9UCEL</t>
+  </si>
+  <si>
+    <t>5AX9UCEL_B0GN8MPYPG</t>
+  </si>
+  <si>
+    <t>5AX9UCEL_B0GN8MFDGZ</t>
+  </si>
+  <si>
+    <t>5BJT4WBR</t>
+  </si>
+  <si>
+    <t>5BJT4WBR_B0GN8MPYPG</t>
+  </si>
+  <si>
+    <t>BOM5</t>
+  </si>
+  <si>
+    <t>5BJT4WBR_B0GN8MFDGZ</t>
+  </si>
+  <si>
+    <t>22QDFZUV</t>
+  </si>
+  <si>
+    <t>22QDFZUV_B0GN8MPYPG</t>
+  </si>
+  <si>
+    <t>22QDFZUV_B0GN8MFDGZ</t>
+  </si>
+  <si>
+    <t>8VGMXDVE</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0G53M9258</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0FQBWV1ST</t>
+  </si>
+  <si>
+    <t>B0FQBWV1ST</t>
+  </si>
+  <si>
+    <t>FBA79840</t>
+  </si>
+  <si>
+    <t>AH-60 RD</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0FQBTRM28</t>
+  </si>
+  <si>
+    <t>B0FQBTRM28</t>
+  </si>
+  <si>
+    <t>FBA79841</t>
+  </si>
+  <si>
+    <t>AH-60 BL</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0FG88HVQ8</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0FF9R3GKK</t>
+  </si>
+  <si>
+    <t>B0FF9R3GKK</t>
+  </si>
+  <si>
+    <t>FBA79783</t>
+  </si>
+  <si>
+    <t>AM-C47</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0D3Q2T5XX</t>
+  </si>
+  <si>
+    <t>B0D3Q2T5XX</t>
+  </si>
+  <si>
+    <t>FBA79356</t>
+  </si>
+  <si>
+    <t>AA-19WL</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0D3M1B4Z8</t>
+  </si>
+  <si>
+    <t>B0D3M1B4Z8</t>
+  </si>
+  <si>
+    <t>FBA79380</t>
+  </si>
+  <si>
+    <t>AM-C46</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0D3LZWTHV</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CQX4GVSB</t>
+  </si>
+  <si>
+    <t>B0CQX4GVSB</t>
+  </si>
+  <si>
+    <t>FBA79579</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CQX3VB1R</t>
+  </si>
+  <si>
+    <t>B0CQX3VB1R</t>
+  </si>
+  <si>
+    <t>FBA79696</t>
+  </si>
+  <si>
+    <t>TD310+</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CM9KJZWQ</t>
+  </si>
+  <si>
+    <t>B0CM9KJZWQ</t>
+  </si>
+  <si>
+    <t>FBA79106</t>
+  </si>
+  <si>
+    <t>AM-C44</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CM6NVLT9</t>
+  </si>
+  <si>
+    <t>B0CM6NVLT9</t>
+  </si>
+  <si>
+    <t>FBA79104</t>
+  </si>
+  <si>
+    <t>AI-11</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CM6NTWBP</t>
+  </si>
+  <si>
+    <t>B0CM6NTWBP</t>
+  </si>
+  <si>
+    <t>FBA79103</t>
+  </si>
+  <si>
+    <t>85437022</t>
+  </si>
+  <si>
+    <t>AI-10</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CKHVHVQ1</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CH4VCD6R</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CH4RNWJX</t>
+  </si>
+  <si>
+    <t>B0CH4RNWJX</t>
+  </si>
+  <si>
+    <t>FBA79011</t>
+  </si>
+  <si>
+    <t>AM-C43</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CH4R1V6S</t>
+  </si>
+  <si>
+    <t>B0CH4R1V6S</t>
+  </si>
+  <si>
+    <t>FBA79016</t>
+  </si>
+  <si>
+    <t>AM-C3a</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CFKZ72N7</t>
+  </si>
+  <si>
+    <t>B0CFKZ72N7</t>
+  </si>
+  <si>
+    <t>FBA79578</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CF5R3V95</t>
+  </si>
+  <si>
+    <t>B0CF5R3V95</t>
+  </si>
+  <si>
+    <t>FBA78973</t>
+  </si>
+  <si>
+    <t>AA-19</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CCVBQRFX</t>
+  </si>
+  <si>
+    <t>B0CCVBQRFX</t>
+  </si>
+  <si>
+    <t>FBA79582</t>
+  </si>
+  <si>
+    <t>TD510+</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CBCB9S14</t>
+  </si>
+  <si>
+    <t>B0CBCB9S14</t>
+  </si>
+  <si>
+    <t>FBA78961</t>
+  </si>
+  <si>
+    <t>AM-C40</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CBCB82MT</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0CBC7QMNV</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0C8JDHLX9</t>
+  </si>
+  <si>
+    <t>B0C8JDHLX9</t>
+  </si>
+  <si>
+    <t>FBA79115</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0C4YT43Z3</t>
+  </si>
+  <si>
+    <t>B0C4YT43Z3</t>
+  </si>
+  <si>
+    <t>FBA78204</t>
+  </si>
+  <si>
+    <t>AM-C31</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BYHHSLPC</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BRKFP94K</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BRKDLXCD</t>
+  </si>
+  <si>
+    <t>B0BRKDLXCD</t>
+  </si>
+  <si>
+    <t>FBA79112</t>
+  </si>
+  <si>
+    <t>T90</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BQ7H7418</t>
+  </si>
+  <si>
+    <t>B0BQ7H7418</t>
+  </si>
+  <si>
+    <t>FBA76597</t>
+  </si>
+  <si>
+    <t>AA-06</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BPLWW72Y</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BLNCP74M</t>
+  </si>
+  <si>
+    <t>B0BLNCP74M</t>
+  </si>
+  <si>
+    <t>FBA76728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM-C25 </t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BLKF46QG</t>
+  </si>
+  <si>
+    <t>B0BLKF46QG</t>
+  </si>
+  <si>
+    <t>FBA76723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM-C20 </t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BLKDC4PP</t>
+  </si>
+  <si>
+    <t>B0BLKDC4PP</t>
+  </si>
+  <si>
+    <t>FBA76722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM-C19 </t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BLKCDRNB</t>
+  </si>
+  <si>
+    <t>B0BLKCDRNB</t>
+  </si>
+  <si>
+    <t>FBA76727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM-C24 </t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BLKB55BM</t>
+  </si>
+  <si>
+    <t>B0BLKB55BM</t>
+  </si>
+  <si>
+    <t>FBA76721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AM-C18 </t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0BLJVJ2GN</t>
+  </si>
+  <si>
+    <t>B0BLJVJ2GN</t>
+  </si>
+  <si>
+    <t>FBA76414</t>
+  </si>
+  <si>
+    <t>AA-05</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4KC7VBM</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4G94VP3</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4G8ZB64</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4G8PH2P</t>
+  </si>
+  <si>
+    <t>B0B4G8PH2P</t>
+  </si>
+  <si>
+    <t>FBA75678</t>
+  </si>
+  <si>
+    <t>AA-01</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4G7VWXD</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4G5ZLTB</t>
+  </si>
+  <si>
+    <t>B0B4G5ZLTB</t>
+  </si>
+  <si>
+    <t>FBA75687</t>
+  </si>
+  <si>
+    <t>AM-W11</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4G59Y8W</t>
+  </si>
+  <si>
+    <t>B0B4G59Y8W</t>
+  </si>
+  <si>
+    <t>FBA75689</t>
+  </si>
+  <si>
+    <t>AM-W13</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4G1PXWV</t>
+  </si>
+  <si>
+    <t>B0B4G1PXWV</t>
+  </si>
+  <si>
+    <t>FBA75680</t>
+  </si>
+  <si>
+    <t>AM-C6</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B0B4DPX2J2</t>
+  </si>
+  <si>
+    <t>B0B4DPX2J2</t>
+  </si>
+  <si>
+    <t>FBA75673</t>
+  </si>
+  <si>
+    <t>AM-C1</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B08NDB5NWP</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B08CVP2HXP</t>
+  </si>
+  <si>
+    <t>B08CVP2HXP</t>
+  </si>
+  <si>
+    <t>FBA77111</t>
+  </si>
+  <si>
+    <t>TC30</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B089SJGQBH</t>
+  </si>
+  <si>
+    <t>B089SJGQBH</t>
+  </si>
+  <si>
+    <t>FBA77104</t>
+  </si>
+  <si>
+    <t>TC20</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B082W4B7SX</t>
+  </si>
+  <si>
+    <t>B082W4B7SX</t>
+  </si>
+  <si>
+    <t>FBA77106</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B07WLWN2ZT</t>
+  </si>
+  <si>
+    <t>B07WLWN2ZT</t>
+  </si>
+  <si>
+    <t>FBA77101</t>
+  </si>
+  <si>
+    <t>TC-777</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B07GVGMW59</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B078WNW4YW</t>
+  </si>
+  <si>
+    <t>B078WNW4YW</t>
+  </si>
+  <si>
+    <t>FBA77117</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>8VGMXDVE_B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>1UJ82ELU</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0FG88HVQ8</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0DT6T6N6B</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0D3LZWTHV</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0CM6NVLT9</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0CH4VCD6R</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0CBCB82MT</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0BPLWW72Y</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B0B4G7VWXD</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B08NDB5NWP</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B07GVGMW59</t>
+  </si>
+  <si>
+    <t>1UJ82ELU_B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>84BS6AXT</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B0CBCB82MT</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B0BYHHSLPC</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B0B4KC7VBM</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B0B4G7VWXD</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B0B4G763WS</t>
+  </si>
+  <si>
+    <t>B0B4G763WS</t>
+  </si>
+  <si>
+    <t>FBA75688</t>
+  </si>
+  <si>
+    <t>AM-W12</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B0B4G1PXWV</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B07GVGMW59</t>
+  </si>
+  <si>
+    <t>84BS6AXT_B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0G53KWRVW</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0FN7B3KWS</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0FG88HVQ8</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0CH4R1V6S</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0CBCB82MT</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0BPLWW72Y</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0B4KC7VBM</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B0B4G1PXWV</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B08NDB5NWP</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B07WLWN2ZT</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B07GVGMW59</t>
+  </si>
+  <si>
+    <t>4WVKA3PQ_B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>1QIWPEFN</t>
+  </si>
+  <si>
+    <t>1QIWPEFN_B0GCP1J2HC</t>
+  </si>
+  <si>
+    <t>1QIWPEFN_B0G53PRM34</t>
+  </si>
+  <si>
+    <t>1QIWPEFN_B0G53M9258</t>
+  </si>
+  <si>
+    <t>1QIWPEFN_B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>1QIWPEFN_B0CH4VCD6R</t>
+  </si>
+  <si>
+    <t>1QIWPEFN_B0B4G8ZB64</t>
   </si>
 </sst>
 </file>
@@ -530,17 +1313,167 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -861,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5A3FE4-F9D3-480E-B305-3F537BEA10CA}">
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P138"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.296875" bestFit="1" customWidth="1"/>
@@ -934,422 +1867,422 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46062</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6">
+        <v>25268223</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K2" s="4">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>4473.88</v>
+      </c>
+      <c r="O2" s="4">
+        <v>4473.88</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="5">
-        <v>46069</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7">
-        <v>25268399</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="4">
-        <v>36</v>
-      </c>
-      <c r="L2" s="4">
-        <v>36</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
-        <v>6431.5</v>
-      </c>
-      <c r="O2" s="4">
-        <v>231534</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D3" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7">
-        <v>25268543</v>
+        <v>46062</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6">
+        <v>25268223</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>30</v>
+        <v>107</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="K3" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L3" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N3" s="4">
-        <v>5942.1</v>
+        <v>1906.14</v>
       </c>
       <c r="O3" s="4">
-        <v>17826.300000000003</v>
+        <v>19061.400000000001</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D4" s="5">
         <v>46076</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7">
-        <v>25268543</v>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6">
+        <v>25268534</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K4" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M4" s="3">
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>1087.07</v>
+        <v>5942.1</v>
       </c>
       <c r="O4" s="4">
-        <v>13044.84</v>
+        <v>17826.300000000003</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D5" s="5">
         <v>46076</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7">
-        <v>25268543</v>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6">
+        <v>25268534</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>35</v>
+        <v>66</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="K5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5" s="4">
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>1481.53</v>
+        <v>8389.1299999999992</v>
       </c>
       <c r="O5" s="4">
-        <v>5926.12</v>
+        <v>25167.39</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D6" s="5">
         <v>46076</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7">
-        <v>25268543</v>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6">
+        <v>25268534</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>44</v>
+        <v>71</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="K6" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>412.5</v>
+        <v>927.11</v>
       </c>
       <c r="O6" s="4">
-        <v>2062.5</v>
+        <v>8343.99</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D7" s="5">
         <v>46076</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7">
-        <v>25268543</v>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6">
+        <v>25268534</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>49</v>
+        <v>26</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K7" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N7" s="4">
-        <v>2568.69</v>
+        <v>1481.53</v>
       </c>
       <c r="O7" s="4">
-        <v>2568.69</v>
+        <v>7407.65</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D8" s="5">
         <v>46076</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7">
-        <v>25268543</v>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6">
+        <v>25268534</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="K8" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L8" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>1683.64</v>
+        <v>412.5</v>
       </c>
       <c r="O8" s="4">
-        <v>11785.480000000001</v>
+        <v>1650</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D9" s="5">
         <v>46076</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7">
-        <v>25268543</v>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6">
+        <v>25268534</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>49</v>
+        <v>37</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="K9" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N9" s="4">
-        <v>571.4</v>
+        <v>1683.64</v>
       </c>
       <c r="O9" s="4">
-        <v>571.4</v>
+        <v>10101.84</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D10" s="5">
         <v>46076</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7">
-        <v>25268543</v>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6">
+        <v>25268534</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="K10" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L10" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
@@ -1358,136 +2291,136 @@
         <v>412.5</v>
       </c>
       <c r="O10" s="4">
-        <v>2475</v>
+        <v>1650</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D11" s="5">
         <v>46076</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7">
-        <v>25268543</v>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6">
+        <v>25268534</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>30</v>
+        <v>79</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="K11" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L11" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M11" s="3">
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>1245.72</v>
+        <v>1751.02</v>
       </c>
       <c r="O11" s="4">
-        <v>6228.6</v>
+        <v>1751.02</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D12" s="5">
         <v>46076</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7">
-        <v>25268543</v>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6">
+        <v>25268534</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>44</v>
+        <v>83</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
       </c>
       <c r="L12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="4">
-        <v>2726</v>
+        <v>1818.39</v>
       </c>
       <c r="O12" s="4">
-        <v>2726</v>
+        <v>1818.39</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D13" s="5">
         <v>46076</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7">
-        <v>25268543</v>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6">
+        <v>25268534</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>18</v>
+        <v>87</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -1499,1051 +2432,1043 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>3145.49</v>
+        <v>1074.28</v>
       </c>
       <c r="O13" s="4">
-        <v>3145.49</v>
+        <v>1074.28</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D14" s="5">
         <v>46076</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7">
-        <v>25268543</v>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6">
+        <v>25268534</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="K14" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>333.05</v>
+        <v>1751.02</v>
       </c>
       <c r="O14" s="4">
-        <v>1332.2</v>
+        <v>5253.0599999999995</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D15" s="5">
         <v>46076</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7">
-        <v>25268543</v>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6">
+        <v>25268534</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>49</v>
+        <v>96</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K15" s="4">
         <v>1</v>
       </c>
       <c r="L15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="4">
-        <v>4683.62</v>
+        <v>1885.77</v>
       </c>
       <c r="O15" s="4">
-        <v>4683.62</v>
+        <v>1885.77</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D16" s="5">
         <v>46076</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7">
-        <v>25268543</v>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6">
+        <v>25268534</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K16" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" s="4">
         <v>0</v>
       </c>
       <c r="M16" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>2121.5700000000002</v>
+        <v>1245.72</v>
       </c>
       <c r="O16" s="4">
-        <v>6364.7100000000009</v>
+        <v>1245.72</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7">
-        <v>25268543</v>
+        <v>46090</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6">
+        <v>25268831</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>18</v>
+        <v>112</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="K17" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L17" s="4">
         <v>0</v>
       </c>
       <c r="M17" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N17" s="4">
-        <v>1245.72</v>
+        <v>6641.25</v>
       </c>
       <c r="O17" s="4">
-        <v>8720.0400000000009</v>
+        <v>13282.5</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7">
-        <v>25268535</v>
+        <v>46090</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6">
+        <v>25268831</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>30</v>
+        <v>116</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="K18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" s="4">
-        <v>5942.1</v>
+        <v>4893.37</v>
       </c>
       <c r="O18" s="4">
-        <v>5942.1</v>
+        <v>9786.74</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7">
-        <v>25268535</v>
+        <v>46090</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6">
+        <v>25268831</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>17</v>
+        <v>120</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="K19" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N19" s="4">
-        <v>1683.64</v>
+        <v>17478.11</v>
       </c>
       <c r="O19" s="4">
-        <v>18520.04</v>
+        <v>34956.22</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="D20" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6">
+        <v>25268831</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>30</v>
+        <v>124</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="K20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" s="4">
-        <v>5942.1</v>
+        <v>9088.2800000000007</v>
       </c>
       <c r="O20" s="4">
-        <v>17826.300000000003</v>
+        <v>18176.560000000001</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="D21" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6">
+        <v>25268831</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>101</v>
+        <v>128</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="K21" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" s="4">
-        <v>8389.1299999999992</v>
+        <v>671.18</v>
       </c>
       <c r="O21" s="4">
-        <v>25167.39</v>
+        <v>1342.36</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="D22" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6">
+        <v>25268831</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>35</v>
+        <v>132</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="K22" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L22" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N22" s="4">
-        <v>927.11</v>
+        <v>1133.9000000000001</v>
       </c>
       <c r="O22" s="4">
-        <v>8343.99</v>
+        <v>5669.5</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D23" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6">
+        <v>25268832</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>35</v>
+        <v>120</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="K23" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N23" s="4">
-        <v>1481.53</v>
+        <v>17478.11</v>
       </c>
       <c r="O23" s="4">
-        <v>7407.65</v>
+        <v>17478.11</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D24" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6">
+        <v>25268832</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>44</v>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="K24" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L24" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="4">
-        <v>412.5</v>
+        <v>1481.53</v>
       </c>
       <c r="O24" s="4">
-        <v>1650</v>
+        <v>1481.53</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D25" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6">
+        <v>25268832</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="K25" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N25" s="4">
-        <v>1683.64</v>
+        <v>412.5</v>
       </c>
       <c r="O25" s="4">
-        <v>10101.84</v>
+        <v>412.5</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D26" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6">
+        <v>25268832</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="K26" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L26" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M26" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N26" s="4">
-        <v>412.5</v>
+        <v>1683.64</v>
       </c>
       <c r="O26" s="4">
-        <v>1650</v>
+        <v>10101.84</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D27" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6">
+        <v>25268832</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>49</v>
+        <v>142</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="K27" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L27" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
       <c r="N27" s="4">
-        <v>1751.02</v>
+        <v>3669.85</v>
       </c>
       <c r="O27" s="4">
-        <v>1751.02</v>
+        <v>14679.4</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D28" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6">
+        <v>25268832</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="I28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="K28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="4">
-        <v>1818.39</v>
+        <v>1074.28</v>
       </c>
       <c r="O28" s="4">
-        <v>1818.39</v>
+        <v>2148.56</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D29" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6">
+        <v>25268832</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>17</v>
+        <v>147</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="K29" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L29" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="4">
-        <v>1074.28</v>
+        <v>1667.8</v>
       </c>
       <c r="O29" s="4">
-        <v>1074.28</v>
+        <v>8339</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D30" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6">
+        <v>25268832</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K30" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L30" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30" s="3">
         <v>0</v>
       </c>
       <c r="N30" s="4">
-        <v>1751.02</v>
+        <v>671.18</v>
       </c>
       <c r="O30" s="4">
-        <v>5253.0599999999995</v>
+        <v>3355.8999999999996</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D31" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7">
-        <v>25268534</v>
+        <v>46090</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6">
+        <v>25268832</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>49</v>
+        <v>132</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K31" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L31" s="4">
         <v>0</v>
       </c>
       <c r="M31" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N31" s="4">
-        <v>1885.77</v>
+        <v>1133.9000000000001</v>
       </c>
       <c r="O31" s="4">
-        <v>1885.77</v>
+        <v>5669.5</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="D32" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7">
-        <v>25268534</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>89</v>
+        <v>46092</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6">
+        <v>25268949</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>18</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="I32" s="6"/>
       <c r="J32" s="4" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="K32" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L32" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="4">
-        <v>1245.72</v>
+        <v>3844.64</v>
       </c>
       <c r="O32" s="4">
-        <v>1245.72</v>
+        <v>11533.92</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D33" s="5">
-        <v>46069</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="7">
-        <v>25268399</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>22</v>
+        <v>46092</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6">
+        <v>25268949</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>18</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="I33" s="6"/>
       <c r="J33" s="4" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="K33" s="4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="L33" s="4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
       </c>
       <c r="N33" s="4">
-        <v>6431.5</v>
+        <v>3495.06</v>
       </c>
       <c r="O33" s="4">
-        <v>231534</v>
+        <v>10485.18</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D34" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7">
-        <v>25268543</v>
+        <v>46092</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6">
+        <v>25268960</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>30</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="I34" s="6"/>
       <c r="J34" s="4" t="s">
-        <v>31</v>
+        <v>166</v>
       </c>
       <c r="K34" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L34" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M34" s="3">
         <v>0</v>
       </c>
       <c r="N34" s="4">
-        <v>5942.1</v>
+        <v>2795.91</v>
       </c>
       <c r="O34" s="4">
-        <v>17826.300000000003</v>
+        <v>33550.92</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D35" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7">
-        <v>25268543</v>
+        <v>46092</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6">
+        <v>25268960</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>35</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I35" s="6"/>
       <c r="J35" s="4" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="K35" s="4">
         <v>12</v>
@@ -2555,379 +3480,363 @@
         <v>0</v>
       </c>
       <c r="N35" s="4">
-        <v>1087.07</v>
+        <v>2795.91</v>
       </c>
       <c r="O35" s="4">
-        <v>13044.84</v>
+        <v>33550.92</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>37</v>
+        <v>172</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D36" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7">
-        <v>25268543</v>
+        <v>46093</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6">
+        <v>25268958</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>35</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I36" s="6"/>
       <c r="J36" s="4" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="K36" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N36" s="4">
-        <v>1481.53</v>
+        <v>3844.64</v>
       </c>
       <c r="O36" s="4">
-        <v>5926.12</v>
+        <v>11533.92</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D37" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7">
-        <v>25268543</v>
+        <v>46093</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6">
+        <v>25268958</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>44</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I37" s="6"/>
       <c r="J37" s="4" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="K37" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L37" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M37" s="3">
         <v>0</v>
       </c>
       <c r="N37" s="4">
-        <v>412.5</v>
+        <v>3495.06</v>
       </c>
       <c r="O37" s="4">
-        <v>2062.5</v>
+        <v>10485.18</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="D38" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7">
-        <v>25268543</v>
+        <v>46093</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6">
+        <v>25268959</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I38" s="6"/>
       <c r="J38" s="4" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="K38" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L38" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
       </c>
       <c r="N38" s="4">
-        <v>2568.69</v>
+        <v>3844.64</v>
       </c>
       <c r="O38" s="4">
-        <v>2568.69</v>
+        <v>11533.92</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="D39" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7">
-        <v>25268543</v>
+        <v>46093</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6">
+        <v>25268959</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>17</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I39" s="6"/>
       <c r="J39" s="4" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="K39" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L39" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M39" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N39" s="4">
-        <v>1683.64</v>
+        <v>3495.06</v>
       </c>
       <c r="O39" s="4">
-        <v>11785.480000000001</v>
+        <v>10485.18</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="D40" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7">
-        <v>25268543</v>
+        <v>46093</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6">
+        <v>25268948</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I40" s="6"/>
       <c r="J40" s="4" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="K40" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L40" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M40" s="3">
         <v>0</v>
       </c>
       <c r="N40" s="4">
-        <v>571.4</v>
+        <v>3844.64</v>
       </c>
       <c r="O40" s="4">
-        <v>571.4</v>
+        <v>11533.92</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="D41" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7">
-        <v>25268543</v>
+        <v>46093</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6">
+        <v>25268948</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>44</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I41" s="6"/>
       <c r="J41" s="4" t="s">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="K41" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L41" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
       <c r="N41" s="4">
-        <v>412.5</v>
+        <v>3495.06</v>
       </c>
       <c r="O41" s="4">
-        <v>2475</v>
+        <v>10485.18</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D42" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7">
-        <v>25268543</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
       <c r="G42" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>30</v>
+        <v>116</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="K42" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L42" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N42" s="4">
-        <v>1245.72</v>
+        <v>4893.37</v>
       </c>
       <c r="O42" s="4">
-        <v>6228.6</v>
+        <v>97867.4</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D43" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7">
-        <v>25268543</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
       <c r="G43" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>44</v>
+        <v>184</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="K43" s="4">
         <v>1</v>
@@ -2939,139 +3848,133 @@
         <v>0</v>
       </c>
       <c r="N43" s="4">
-        <v>2726</v>
+        <v>1548.9</v>
       </c>
       <c r="O43" s="4">
-        <v>2726</v>
+        <v>1548.9</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>71</v>
+        <v>187</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D44" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7">
-        <v>25268543</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
       <c r="G44" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>18</v>
+        <v>188</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="K44" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L44" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
       <c r="N44" s="4">
-        <v>3145.49</v>
+        <v>1548.9</v>
       </c>
       <c r="O44" s="4">
-        <v>3145.49</v>
+        <v>4646.7000000000007</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D45" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7">
-        <v>25268543</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>78</v>
+      <c r="H45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="K45" s="4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L45" s="4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
       <c r="N45" s="4">
-        <v>333.05</v>
+        <v>1481.53</v>
       </c>
       <c r="O45" s="4">
-        <v>1332.2</v>
+        <v>26667.54</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D46" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7">
-        <v>25268543</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
       <c r="G46" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>49</v>
+        <v>193</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="K46" s="4">
         <v>1</v>
@@ -3083,139 +3986,133 @@
         <v>0</v>
       </c>
       <c r="N46" s="4">
-        <v>4683.62</v>
+        <v>2222.63</v>
       </c>
       <c r="O46" s="4">
-        <v>4683.62</v>
+        <v>2222.63</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D47" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7">
-        <v>25268543</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
       <c r="G47" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>49</v>
+        <v>197</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="K47" s="4">
         <v>3</v>
       </c>
       <c r="L47" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M47" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N47" s="4">
-        <v>2121.5700000000002</v>
+        <v>3202.75</v>
       </c>
       <c r="O47" s="4">
-        <v>6364.7100000000009</v>
+        <v>9608.25</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="D48" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7">
-        <v>25268543</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
       <c r="G48" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>18</v>
+        <v>201</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>91</v>
+        <v>203</v>
       </c>
       <c r="K48" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L48" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M48" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N48" s="4">
-        <v>1245.72</v>
+        <v>2656.08</v>
       </c>
       <c r="O48" s="4">
-        <v>8720.0400000000009</v>
+        <v>13280.4</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="D49" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7">
-        <v>25268535</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
       <c r="G49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K49" s="4">
         <v>1</v>
@@ -3227,385 +4124,369 @@
         <v>0</v>
       </c>
       <c r="N49" s="4">
-        <v>5942.1</v>
+        <v>2568.69</v>
       </c>
       <c r="O49" s="4">
-        <v>5942.1</v>
+        <v>2568.69</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="D50" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7">
-        <v>25268535</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6"/>
       <c r="G50" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I50" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I50" s="6" t="s">
         <v>17</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="K50" s="4">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="L50" s="4">
         <v>0</v>
       </c>
       <c r="M50" s="3">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="N50" s="4">
         <v>1683.64</v>
       </c>
       <c r="O50" s="4">
-        <v>18520.04</v>
+        <v>92600.200000000012</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D51" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6"/>
       <c r="G51" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>30</v>
+        <v>207</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>31</v>
+        <v>209</v>
       </c>
       <c r="K51" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L51" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="4">
-        <v>5942.1</v>
+        <v>1616.28</v>
       </c>
       <c r="O51" s="4">
-        <v>17826.300000000003</v>
+        <v>1616.28</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D52" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
       <c r="G52" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>101</v>
+        <v>211</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="K52" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L52" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M52" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N52" s="4">
-        <v>8389.1299999999992</v>
+        <v>1751.02</v>
       </c>
       <c r="O52" s="4">
-        <v>25167.39</v>
+        <v>10506.119999999999</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D53" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6"/>
       <c r="G53" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>35</v>
+        <v>215</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="K53" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L53" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
       </c>
       <c r="N53" s="4">
-        <v>927.11</v>
+        <v>3564.98</v>
       </c>
       <c r="O53" s="4">
-        <v>8343.99</v>
+        <v>3564.98</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D54" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6"/>
       <c r="G54" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>35</v>
+        <v>219</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>40</v>
+        <v>221</v>
       </c>
       <c r="K54" s="4">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L54" s="4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M54" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N54" s="4">
-        <v>1481.53</v>
+        <v>1087.07</v>
       </c>
       <c r="O54" s="4">
-        <v>7407.65</v>
+        <v>19567.259999999998</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>108</v>
+        <v>222</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D55" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6"/>
       <c r="G55" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>44</v>
+        <v>223</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>225</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>45</v>
+        <v>226</v>
       </c>
       <c r="K55" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L55" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
       </c>
       <c r="N55" s="4">
-        <v>412.5</v>
+        <v>2460.3200000000002</v>
       </c>
       <c r="O55" s="4">
-        <v>1650</v>
+        <v>12301.6</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>109</v>
+        <v>227</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D56" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6"/>
       <c r="G56" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>17</v>
+        <v>142</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="K56" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L56" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N56" s="4">
-        <v>1683.64</v>
+        <v>3669.85</v>
       </c>
       <c r="O56" s="4">
-        <v>10101.84</v>
+        <v>7339.7</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D57" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6"/>
       <c r="G57" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="K57" s="4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L57" s="4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -3614,232 +4495,222 @@
         <v>412.5</v>
       </c>
       <c r="O57" s="4">
-        <v>1650</v>
+        <v>5775</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D58" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6"/>
       <c r="G58" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>49</v>
+        <v>230</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>114</v>
+        <v>232</v>
       </c>
       <c r="K58" s="4">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L58" s="4">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="4">
-        <v>1751.02</v>
+        <v>1818.39</v>
       </c>
       <c r="O58" s="4">
-        <v>1751.02</v>
+        <v>43641.36</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>115</v>
+        <v>233</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D59" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6"/>
       <c r="G59" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>17</v>
+        <v>234</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="K59" s="4">
         <v>1</v>
       </c>
       <c r="L59" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" s="4">
-        <v>1818.39</v>
+        <v>575.21</v>
       </c>
       <c r="O59" s="4">
-        <v>1818.39</v>
+        <v>575.21</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D60" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6"/>
       <c r="G60" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>17</v>
+        <v>238</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>122</v>
+        <v>240</v>
       </c>
       <c r="K60" s="4">
         <v>1</v>
       </c>
       <c r="L60" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" s="4">
-        <v>1074.28</v>
+        <v>2460.3200000000002</v>
       </c>
       <c r="O60" s="4">
-        <v>1074.28</v>
+        <v>2460.3200000000002</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>123</v>
+        <v>241</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D61" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6"/>
       <c r="G61" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>126</v>
+        <v>242</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="K61" s="4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L61" s="4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="4">
-        <v>1751.02</v>
+        <v>2535.38</v>
       </c>
       <c r="O61" s="4">
-        <v>5253.0599999999995</v>
+        <v>32959.94</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>128</v>
+        <v>245</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="D62" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7">
-        <v>25268534</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6"/>
       <c r="G62" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I62" s="7" t="s">
-        <v>49</v>
+        <v>246</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>131</v>
+        <v>248</v>
       </c>
       <c r="K62" s="4">
         <v>1</v>
@@ -3851,67 +4722,3538 @@
         <v>1</v>
       </c>
       <c r="N62" s="4">
-        <v>1885.77</v>
+        <v>4543.79</v>
       </c>
       <c r="O62" s="4">
-        <v>1885.77</v>
+        <v>4543.79</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D63" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="K63" s="4">
+        <v>1</v>
+      </c>
+      <c r="L63" s="4">
+        <v>1</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O63" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D64" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K64" s="4">
+        <v>1</v>
+      </c>
+      <c r="L64" s="4">
+        <v>1</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="O64" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D65" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K65" s="4">
+        <v>1</v>
+      </c>
+      <c r="L65" s="4">
+        <v>1</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="4">
+        <v>2726</v>
+      </c>
+      <c r="O65" s="4">
+        <v>2726</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D66" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="K66" s="4">
+        <v>7</v>
+      </c>
+      <c r="L66" s="4">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3">
+        <v>7</v>
+      </c>
+      <c r="N66" s="4">
+        <v>1270.55</v>
+      </c>
+      <c r="O66" s="4">
+        <v>8893.85</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D67" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>0</v>
+      </c>
+      <c r="M67" s="3">
+        <v>1</v>
+      </c>
+      <c r="N67" s="4">
+        <v>1683.65</v>
+      </c>
+      <c r="O67" s="4">
+        <v>1683.65</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K68" s="4">
+        <v>1</v>
+      </c>
+      <c r="L68" s="4">
+        <v>1</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O68" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D69" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K69" s="4">
+        <v>7</v>
+      </c>
+      <c r="L69" s="4">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>7</v>
+      </c>
+      <c r="N69" s="4">
+        <v>1818.39</v>
+      </c>
+      <c r="O69" s="4">
+        <v>12728.730000000001</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D70" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K70" s="4">
+        <v>1</v>
+      </c>
+      <c r="L70" s="4">
+        <v>1</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="4">
+        <v>3145.49</v>
+      </c>
+      <c r="O70" s="4">
+        <v>3145.49</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D71" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K71" s="4">
+        <v>8</v>
+      </c>
+      <c r="L71" s="4">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>8</v>
+      </c>
+      <c r="N71" s="4">
+        <v>2859.53</v>
+      </c>
+      <c r="O71" s="4">
+        <v>22876.240000000002</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D72" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="K72" s="4">
+        <v>1</v>
+      </c>
+      <c r="L72" s="4">
+        <v>1</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4">
+        <v>933.69</v>
+      </c>
+      <c r="O72" s="4">
+        <v>933.69</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D73" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K73" s="4">
+        <v>9</v>
+      </c>
+      <c r="L73" s="4">
+        <v>9</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="4">
+        <v>1074.28</v>
+      </c>
+      <c r="O73" s="4">
+        <v>9668.52</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D74" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E74" s="5"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="K74" s="4">
+        <v>1</v>
+      </c>
+      <c r="L74" s="4">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>1</v>
+      </c>
+      <c r="N74" s="4">
+        <v>1626.38</v>
+      </c>
+      <c r="O74" s="4">
+        <v>1626.38</v>
+      </c>
+      <c r="P74" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D75" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E75" s="5"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="K75" s="4">
+        <v>1</v>
+      </c>
+      <c r="L75" s="4">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>1</v>
+      </c>
+      <c r="N75" s="4">
+        <v>939.91</v>
+      </c>
+      <c r="O75" s="4">
+        <v>939.91</v>
+      </c>
+      <c r="P75" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D76" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E76" s="5"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K76" s="4">
+        <v>1</v>
+      </c>
+      <c r="L76" s="4">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3">
+        <v>1</v>
+      </c>
+      <c r="N76" s="4">
+        <v>1272.67</v>
+      </c>
+      <c r="O76" s="4">
+        <v>1272.67</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D77" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E77" s="5"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K77" s="4">
+        <v>1</v>
+      </c>
+      <c r="L77" s="4">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>1</v>
+      </c>
+      <c r="N77" s="4">
+        <v>1074.28</v>
+      </c>
+      <c r="O77" s="4">
+        <v>1074.28</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D78" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E78" s="5"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="K78" s="4">
+        <v>1</v>
+      </c>
+      <c r="L78" s="4">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3">
+        <v>1</v>
+      </c>
+      <c r="N78" s="4">
+        <v>1683.65</v>
+      </c>
+      <c r="O78" s="4">
+        <v>1683.65</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D79" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E79" s="5"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="K79" s="4">
+        <v>129</v>
+      </c>
+      <c r="L79" s="4">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3">
+        <v>129</v>
+      </c>
+      <c r="N79" s="4">
+        <v>466.53</v>
+      </c>
+      <c r="O79" s="4">
+        <v>60182.369999999995</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D80" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E80" s="5"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K80" s="4">
+        <v>5</v>
+      </c>
+      <c r="L80" s="4">
+        <v>5</v>
+      </c>
+      <c r="M80" s="3">
+        <v>0</v>
+      </c>
+      <c r="N80" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O80" s="4">
+        <v>8755.1</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D81" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E81" s="5"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K81" s="4">
+        <v>6</v>
+      </c>
+      <c r="L81" s="4">
+        <v>6</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="4">
+        <v>333.05</v>
+      </c>
+      <c r="O81" s="4">
+        <v>1998.3000000000002</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D82" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E82" s="5"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K82" s="4">
+        <v>6</v>
+      </c>
+      <c r="L82" s="4">
+        <v>6</v>
+      </c>
+      <c r="M82" s="3">
+        <v>0</v>
+      </c>
+      <c r="N82" s="4">
+        <v>671.18</v>
+      </c>
+      <c r="O82" s="4">
+        <v>4027.08</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D83" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E83" s="5"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="K83" s="4">
+        <v>5</v>
+      </c>
+      <c r="L83" s="4">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="4">
+        <v>1467.58</v>
+      </c>
+      <c r="O83" s="4">
+        <v>7337.9</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D84" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E84" s="5"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="H84" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="K84" s="4">
+        <v>15</v>
+      </c>
+      <c r="L84" s="4">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>15</v>
+      </c>
+      <c r="N84" s="4">
+        <v>1133.9000000000001</v>
+      </c>
+      <c r="O84" s="4">
+        <v>17008.5</v>
+      </c>
+      <c r="P84" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D85" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E85" s="5"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="K85" s="4">
+        <v>1</v>
+      </c>
+      <c r="L85" s="4">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>1</v>
+      </c>
+      <c r="N85" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="O85" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="P85" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D86" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E86" s="5"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="K86" s="4">
+        <v>1</v>
+      </c>
+      <c r="L86" s="4">
+        <v>1</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="4">
+        <v>1616.28</v>
+      </c>
+      <c r="O86" s="4">
+        <v>1616.28</v>
+      </c>
+      <c r="P86" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D87" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E87" s="5"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="K87" s="4">
+        <v>1</v>
+      </c>
+      <c r="L87" s="4">
+        <v>1</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="4">
+        <v>1548.9</v>
+      </c>
+      <c r="O87" s="4">
+        <v>1548.9</v>
+      </c>
+      <c r="P87" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D88" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E88" s="5"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="K88" s="4">
+        <v>74</v>
+      </c>
+      <c r="L88" s="4">
+        <v>74</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="4">
+        <v>1919.45</v>
+      </c>
+      <c r="O88" s="4">
+        <v>142039.30000000002</v>
+      </c>
+      <c r="P88" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D89" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E89" s="5"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K89" s="4">
+        <v>3</v>
+      </c>
+      <c r="L89" s="4">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>3</v>
+      </c>
+      <c r="N89" s="4">
+        <v>2121.5700000000002</v>
+      </c>
+      <c r="O89" s="4">
+        <v>6364.7100000000009</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D90" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E90" s="5"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K90" s="4">
+        <v>3</v>
+      </c>
+      <c r="L90" s="4">
+        <v>3</v>
+      </c>
+      <c r="M90" s="3">
+        <v>0</v>
+      </c>
+      <c r="N90" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O90" s="4">
+        <v>5253.0599999999995</v>
+      </c>
+      <c r="P90" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D91" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E91" s="5"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="K91" s="4">
+        <v>1</v>
+      </c>
+      <c r="L91" s="4">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>1</v>
+      </c>
+      <c r="N91" s="4">
+        <v>3669.85</v>
+      </c>
+      <c r="O91" s="4">
+        <v>3669.85</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D92" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E92" s="5"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="K92" s="4">
+        <v>2</v>
+      </c>
+      <c r="L92" s="4">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>2</v>
+      </c>
+      <c r="N92" s="4">
+        <v>1651.91</v>
+      </c>
+      <c r="O92" s="4">
+        <v>3303.82</v>
+      </c>
+      <c r="P92" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D93" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E93" s="5"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K93" s="4">
+        <v>2</v>
+      </c>
+      <c r="L93" s="4">
+        <v>2</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="4">
+        <v>1683.65</v>
+      </c>
+      <c r="O93" s="4">
+        <v>3367.3</v>
+      </c>
+      <c r="P93" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D94" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E94" s="5"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D63" s="5">
-        <v>46076</v>
-      </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7">
-        <v>25268534</v>
-      </c>
-      <c r="G63" s="4" t="s">
+      <c r="I94" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K94" s="4">
+        <v>8</v>
+      </c>
+      <c r="L94" s="4">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>8</v>
+      </c>
+      <c r="N94" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="O94" s="4">
+        <v>15086.16</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D95" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E95" s="5"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="K95" s="4">
+        <v>1</v>
+      </c>
+      <c r="L95" s="4">
+        <v>1</v>
+      </c>
+      <c r="M95" s="3">
+        <v>0</v>
+      </c>
+      <c r="N95" s="4">
+        <v>1747.25</v>
+      </c>
+      <c r="O95" s="4">
+        <v>1747.25</v>
+      </c>
+      <c r="P95" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E96" s="5"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K96" s="4">
+        <v>26</v>
+      </c>
+      <c r="L96" s="4">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>26</v>
+      </c>
+      <c r="N96" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="O96" s="4">
+        <v>32388.720000000001</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D97" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E97" s="5"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K97" s="4">
+        <v>15</v>
+      </c>
+      <c r="L97" s="4">
+        <v>3</v>
+      </c>
+      <c r="M97" s="3">
+        <v>12</v>
+      </c>
+      <c r="N97" s="4">
+        <v>1481.53</v>
+      </c>
+      <c r="O97" s="4">
+        <v>22222.95</v>
+      </c>
+      <c r="P97" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D98" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E98" s="5"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K98" s="4">
+        <v>1</v>
+      </c>
+      <c r="L98" s="4">
+        <v>1</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="4">
+        <v>412.5</v>
+      </c>
+      <c r="O98" s="4">
+        <v>412.5</v>
+      </c>
+      <c r="P98" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D99" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E99" s="5"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K99" s="4">
+        <v>1</v>
+      </c>
+      <c r="L99" s="4">
+        <v>1</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="4">
+        <v>2568.69</v>
+      </c>
+      <c r="O99" s="4">
+        <v>2568.69</v>
+      </c>
+      <c r="P99" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D100" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E100" s="5"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K100" s="4">
+        <v>5</v>
+      </c>
+      <c r="L100" s="4">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>5</v>
+      </c>
+      <c r="N100" s="4">
+        <v>1683.64</v>
+      </c>
+      <c r="O100" s="4">
+        <v>8418.2000000000007</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D101" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K101" s="4">
+        <v>16</v>
+      </c>
+      <c r="L101" s="4">
+        <v>16</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="4">
+        <v>1087.07</v>
+      </c>
+      <c r="O101" s="4">
+        <v>17393.12</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D102" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E102" s="5"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K102" s="4">
+        <v>2</v>
+      </c>
+      <c r="L102" s="4">
+        <v>2</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="4">
+        <v>412.5</v>
+      </c>
+      <c r="O102" s="4">
+        <v>825</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K103" s="4">
+        <v>1</v>
+      </c>
+      <c r="L103" s="4">
+        <v>1</v>
+      </c>
+      <c r="M103" s="3">
+        <v>0</v>
+      </c>
+      <c r="N103" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="O103" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="P103" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D104" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E104" s="5"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K104" s="4">
+        <v>2</v>
+      </c>
+      <c r="L104" s="4">
+        <v>0</v>
+      </c>
+      <c r="M104" s="3">
+        <v>2</v>
+      </c>
+      <c r="N104" s="4">
+        <v>1818.39</v>
+      </c>
+      <c r="O104" s="4">
+        <v>3636.78</v>
+      </c>
+      <c r="P104" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D105" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E105" s="5"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H63" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I63" s="7" t="s">
+      <c r="K105" s="4">
+        <v>2</v>
+      </c>
+      <c r="L105" s="4">
+        <v>2</v>
+      </c>
+      <c r="M105" s="3">
+        <v>0</v>
+      </c>
+      <c r="N105" s="4">
+        <v>1074.28</v>
+      </c>
+      <c r="O105" s="4">
+        <v>2148.56</v>
+      </c>
+      <c r="P105" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D106" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E106" s="5"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="K106" s="4">
+        <v>5</v>
+      </c>
+      <c r="L106" s="4">
+        <v>0</v>
+      </c>
+      <c r="M106" s="3">
+        <v>5</v>
+      </c>
+      <c r="N106" s="4">
+        <v>1133.9000000000001</v>
+      </c>
+      <c r="O106" s="4">
+        <v>5669.5</v>
+      </c>
+      <c r="P106" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D107" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E107" s="5"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K107" s="4">
+        <v>1</v>
+      </c>
+      <c r="L107" s="4">
+        <v>0</v>
+      </c>
+      <c r="M107" s="3">
+        <v>1</v>
+      </c>
+      <c r="N107" s="4">
+        <v>2121.5700000000002</v>
+      </c>
+      <c r="O107" s="4">
+        <v>2121.5700000000002</v>
+      </c>
+      <c r="P107" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D108" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E108" s="5"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K108" s="4">
+        <v>1</v>
+      </c>
+      <c r="L108" s="4">
+        <v>0</v>
+      </c>
+      <c r="M108" s="3">
+        <v>1</v>
+      </c>
+      <c r="N108" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="O108" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="P108" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D109" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E109" s="5"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I109" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J63" s="4" t="s">
+      <c r="J109" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K109" s="4">
+        <v>1</v>
+      </c>
+      <c r="L109" s="4">
+        <v>0</v>
+      </c>
+      <c r="M109" s="3">
+        <v>1</v>
+      </c>
+      <c r="N109" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="O109" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="P109" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D110" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E110" s="5"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K110" s="4">
+        <v>7</v>
+      </c>
+      <c r="L110" s="4">
+        <v>0</v>
+      </c>
+      <c r="M110" s="3">
+        <v>7</v>
+      </c>
+      <c r="N110" s="4">
+        <v>1683.64</v>
+      </c>
+      <c r="O110" s="4">
+        <v>11785.480000000001</v>
+      </c>
+      <c r="P110" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D111" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E111" s="5"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K111" s="4">
+        <v>2</v>
+      </c>
+      <c r="L111" s="4">
+        <v>2</v>
+      </c>
+      <c r="M111" s="3">
+        <v>0</v>
+      </c>
+      <c r="N111" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="O111" s="4">
+        <v>2491.44</v>
+      </c>
+      <c r="P111" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D112" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E112" s="5"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K112" s="4">
+        <v>1</v>
+      </c>
+      <c r="L112" s="4">
+        <v>1</v>
+      </c>
+      <c r="M112" s="3">
+        <v>0</v>
+      </c>
+      <c r="N112" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O112" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="P112" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D113" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E113" s="5"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="K63" s="4">
-        <v>1</v>
-      </c>
-      <c r="L63" s="4">
-        <v>0</v>
-      </c>
-      <c r="M63" s="3">
-        <v>1</v>
-      </c>
-      <c r="N63" s="4">
+      <c r="H113" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K113" s="4">
+        <v>3</v>
+      </c>
+      <c r="L113" s="4">
+        <v>3</v>
+      </c>
+      <c r="M113" s="3">
+        <v>0</v>
+      </c>
+      <c r="N113" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O113" s="4">
+        <v>5253.0599999999995</v>
+      </c>
+      <c r="P113" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D114" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E114" s="5"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="K114" s="4">
+        <v>5</v>
+      </c>
+      <c r="L114" s="4">
+        <v>0</v>
+      </c>
+      <c r="M114" s="3">
+        <v>5</v>
+      </c>
+      <c r="N114" s="4">
+        <v>1133.9000000000001</v>
+      </c>
+      <c r="O114" s="4">
+        <v>5669.5</v>
+      </c>
+      <c r="P114" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D115" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E115" s="5"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="K115" s="4">
+        <v>1</v>
+      </c>
+      <c r="L115" s="4">
+        <v>1</v>
+      </c>
+      <c r="M115" s="3">
+        <v>0</v>
+      </c>
+      <c r="N115" s="4">
+        <v>2935.74</v>
+      </c>
+      <c r="O115" s="4">
+        <v>2935.74</v>
+      </c>
+      <c r="P115" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D116" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E116" s="5"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="K116" s="4">
+        <v>1</v>
+      </c>
+      <c r="L116" s="4">
+        <v>1</v>
+      </c>
+      <c r="M116" s="3">
+        <v>0</v>
+      </c>
+      <c r="N116" s="4">
+        <v>1548.9</v>
+      </c>
+      <c r="O116" s="4">
+        <v>1548.9</v>
+      </c>
+      <c r="P116" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D117" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E117" s="5"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K117" s="4">
+        <v>2</v>
+      </c>
+      <c r="L117" s="4">
+        <v>0</v>
+      </c>
+      <c r="M117" s="3">
+        <v>2</v>
+      </c>
+      <c r="N117" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="O117" s="4">
+        <v>3771.54</v>
+      </c>
+      <c r="P117" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D118" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E118" s="5"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K118" s="4">
+        <v>11</v>
+      </c>
+      <c r="L118" s="4">
+        <v>0</v>
+      </c>
+      <c r="M118" s="3">
+        <v>11</v>
+      </c>
+      <c r="N118" s="4">
         <v>1245.72</v>
       </c>
-      <c r="O63" s="4">
+      <c r="O118" s="4">
+        <v>13702.92</v>
+      </c>
+      <c r="P118" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D119" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E119" s="5"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K119" s="4">
+        <v>2</v>
+      </c>
+      <c r="L119" s="4">
+        <v>0</v>
+      </c>
+      <c r="M119" s="3">
+        <v>2</v>
+      </c>
+      <c r="N119" s="4">
+        <v>8389.1299999999992</v>
+      </c>
+      <c r="O119" s="4">
+        <v>16778.259999999998</v>
+      </c>
+      <c r="P119" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D120" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E120" s="5"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I120" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="K120" s="4">
+        <v>2</v>
+      </c>
+      <c r="L120" s="4">
+        <v>0</v>
+      </c>
+      <c r="M120" s="3">
+        <v>2</v>
+      </c>
+      <c r="N120" s="4">
+        <v>9088.2800000000007</v>
+      </c>
+      <c r="O120" s="4">
+        <v>18176.560000000001</v>
+      </c>
+      <c r="P120" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D121" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E121" s="5"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K121" s="4">
+        <v>99</v>
+      </c>
+      <c r="L121" s="4">
+        <v>0</v>
+      </c>
+      <c r="M121" s="3">
+        <v>99</v>
+      </c>
+      <c r="N121" s="4">
+        <v>1481.53</v>
+      </c>
+      <c r="O121" s="4">
+        <v>146671.47</v>
+      </c>
+      <c r="P121" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D122" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E122" s="5"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I122" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K122" s="4">
+        <v>4</v>
+      </c>
+      <c r="L122" s="4">
+        <v>0</v>
+      </c>
+      <c r="M122" s="3">
+        <v>4</v>
+      </c>
+      <c r="N122" s="4">
+        <v>1683.64</v>
+      </c>
+      <c r="O122" s="4">
+        <v>6734.56</v>
+      </c>
+      <c r="P122" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D123" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E123" s="5"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="K123" s="4">
+        <v>1</v>
+      </c>
+      <c r="L123" s="4">
+        <v>1</v>
+      </c>
+      <c r="M123" s="3">
+        <v>0</v>
+      </c>
+      <c r="N123" s="4">
+        <v>575.21</v>
+      </c>
+      <c r="O123" s="4">
+        <v>575.21</v>
+      </c>
+      <c r="P123" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D124" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E124" s="5"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I124" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J124" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K124" s="4">
+        <v>3</v>
+      </c>
+      <c r="L124" s="4">
+        <v>3</v>
+      </c>
+      <c r="M124" s="3">
+        <v>0</v>
+      </c>
+      <c r="N124" s="4">
         <v>1245.72</v>
       </c>
-      <c r="P63" s="3" t="s">
-        <v>133</v>
+      <c r="O124" s="4">
+        <v>3737.16</v>
+      </c>
+      <c r="P124" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D125" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E125" s="5"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I125" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K125" s="4">
+        <v>11</v>
+      </c>
+      <c r="L125" s="4">
+        <v>0</v>
+      </c>
+      <c r="M125" s="3">
+        <v>11</v>
+      </c>
+      <c r="N125" s="4">
+        <v>1818.39</v>
+      </c>
+      <c r="O125" s="4">
+        <v>20002.29</v>
+      </c>
+      <c r="P125" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D126" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E126" s="5"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I126" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K126" s="4">
+        <v>5</v>
+      </c>
+      <c r="L126" s="4">
+        <v>5</v>
+      </c>
+      <c r="M126" s="3">
+        <v>0</v>
+      </c>
+      <c r="N126" s="4">
+        <v>1074.28</v>
+      </c>
+      <c r="O126" s="4">
+        <v>5371.4</v>
+      </c>
+      <c r="P126" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D127" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E127" s="5"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I127" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K127" s="4">
+        <v>11</v>
+      </c>
+      <c r="L127" s="4">
+        <v>11</v>
+      </c>
+      <c r="M127" s="3">
+        <v>0</v>
+      </c>
+      <c r="N127" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O127" s="4">
+        <v>19261.22</v>
+      </c>
+      <c r="P127" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D128" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E128" s="5"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="K128" s="4">
+        <v>2</v>
+      </c>
+      <c r="L128" s="4">
+        <v>2</v>
+      </c>
+      <c r="M128" s="3">
+        <v>0</v>
+      </c>
+      <c r="N128" s="4">
+        <v>1548.9</v>
+      </c>
+      <c r="O128" s="4">
+        <v>3097.8</v>
+      </c>
+      <c r="P128" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D129" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E129" s="5"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K129" s="4">
+        <v>5</v>
+      </c>
+      <c r="L129" s="4">
+        <v>0</v>
+      </c>
+      <c r="M129" s="3">
+        <v>5</v>
+      </c>
+      <c r="N129" s="4">
+        <v>2121.5700000000002</v>
+      </c>
+      <c r="O129" s="4">
+        <v>10607.85</v>
+      </c>
+      <c r="P129" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D130" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E130" s="5"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="I130" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J130" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K130" s="4">
+        <v>1</v>
+      </c>
+      <c r="L130" s="4">
+        <v>1</v>
+      </c>
+      <c r="M130" s="3">
+        <v>0</v>
+      </c>
+      <c r="N130" s="4">
+        <v>1683.65</v>
+      </c>
+      <c r="O130" s="4">
+        <v>1683.65</v>
+      </c>
+      <c r="P130" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D131" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E131" s="5"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I131" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J131" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K131" s="4">
+        <v>13</v>
+      </c>
+      <c r="L131" s="4">
+        <v>0</v>
+      </c>
+      <c r="M131" s="3">
+        <v>13</v>
+      </c>
+      <c r="N131" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="O131" s="4">
+        <v>24515.01</v>
+      </c>
+      <c r="P131" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D132" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E132" s="5"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I132" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K132" s="4">
+        <v>32</v>
+      </c>
+      <c r="L132" s="4">
+        <v>0</v>
+      </c>
+      <c r="M132" s="3">
+        <v>32</v>
+      </c>
+      <c r="N132" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="O132" s="4">
+        <v>39863.040000000001</v>
+      </c>
+      <c r="P132" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D133" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E133" s="5"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K133" s="4">
+        <v>4</v>
+      </c>
+      <c r="L133" s="4">
+        <v>0</v>
+      </c>
+      <c r="M133" s="3">
+        <v>4</v>
+      </c>
+      <c r="N133" s="4">
+        <v>5942.1</v>
+      </c>
+      <c r="O133" s="4">
+        <v>23768.400000000001</v>
+      </c>
+      <c r="P133" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D134" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E134" s="5"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J134" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K134" s="4">
+        <v>1</v>
+      </c>
+      <c r="L134" s="4">
+        <v>0</v>
+      </c>
+      <c r="M134" s="3">
+        <v>1</v>
+      </c>
+      <c r="N134" s="4">
+        <v>6641.25</v>
+      </c>
+      <c r="O134" s="4">
+        <v>6641.25</v>
+      </c>
+      <c r="P134" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D135" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E135" s="5"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I135" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J135" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K135" s="4">
+        <v>3</v>
+      </c>
+      <c r="L135" s="4">
+        <v>0</v>
+      </c>
+      <c r="M135" s="3">
+        <v>3</v>
+      </c>
+      <c r="N135" s="4">
+        <v>4893.37</v>
+      </c>
+      <c r="O135" s="4">
+        <v>14680.11</v>
+      </c>
+      <c r="P135" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D136" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E136" s="5"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I136" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K136" s="4">
+        <v>8</v>
+      </c>
+      <c r="L136" s="4">
+        <v>0</v>
+      </c>
+      <c r="M136" s="3">
+        <v>8</v>
+      </c>
+      <c r="N136" s="4">
+        <v>1683.64</v>
+      </c>
+      <c r="O136" s="4">
+        <v>13469.12</v>
+      </c>
+      <c r="P136" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D137" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E137" s="5"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I137" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K137" s="4">
+        <v>12</v>
+      </c>
+      <c r="L137" s="4">
+        <v>12</v>
+      </c>
+      <c r="M137" s="3">
+        <v>0</v>
+      </c>
+      <c r="N137" s="4">
+        <v>412.5</v>
+      </c>
+      <c r="O137" s="4">
+        <v>4950</v>
+      </c>
+      <c r="P137" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D138" s="5">
+        <v>46097</v>
+      </c>
+      <c r="E138" s="5"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I138" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J138" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="K138" s="4">
+        <v>1</v>
+      </c>
+      <c r="L138" s="4">
+        <v>1</v>
+      </c>
+      <c r="M138" s="3">
+        <v>0</v>
+      </c>
+      <c r="N138" s="4">
+        <v>671.18</v>
+      </c>
+      <c r="O138" s="4">
+        <v>671.18</v>
+      </c>
+      <c r="P138" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P63" xr:uid="{AD5A3FE4-F9D3-480E-B305-3F537BEA10CA}"/>
-  <conditionalFormatting sqref="B2:B63">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <autoFilter ref="A1:P1" xr:uid="{AD5A3FE4-F9D3-480E-B305-3F537BEA10CA}"/>
+  <conditionalFormatting sqref="B2:B138">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B109:B138">
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B118:B138">
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B132:B138">
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B138">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/In_Transit_PO data.xlsx
+++ b/data/input/In_Transit_PO data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16B7B0B-03FD-4B04-A67B-4CD9F4EAED5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98A923B-2256-456C-B56F-AD4CA79FDB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED1C42A4-610F-4493-A647-7EDE7899E1B2}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="337">
   <si>
     <t>PO Number</t>
   </si>
@@ -96,15 +96,6 @@
     <t>In-Transit</t>
   </si>
   <si>
-    <t>B0GCP1J2HC</t>
-  </si>
-  <si>
-    <t>FBA79972</t>
-  </si>
-  <si>
-    <t>M8</t>
-  </si>
-  <si>
     <t>B0FG88HVQ8</t>
   </si>
   <si>
@@ -114,15 +105,6 @@
     <t>AH-50</t>
   </si>
   <si>
-    <t>B0DT6T6N6B</t>
-  </si>
-  <si>
-    <t>FBA79694</t>
-  </si>
-  <si>
-    <t>AA-26</t>
-  </si>
-  <si>
     <t>B0CBCB82MT</t>
   </si>
   <si>
@@ -162,15 +144,6 @@
     <t>AM-Mix10</t>
   </si>
   <si>
-    <t>B0BYHHSLPC</t>
-  </si>
-  <si>
-    <t>FBA79116</t>
-  </si>
-  <si>
-    <t>TC-777 PRO</t>
-  </si>
-  <si>
     <t>B0B4KC7VBM</t>
   </si>
   <si>
@@ -180,15 +153,6 @@
     <t>AM-C5</t>
   </si>
   <si>
-    <t>B0G53M9258</t>
-  </si>
-  <si>
-    <t>FBA79968</t>
-  </si>
-  <si>
-    <t>AI-14</t>
-  </si>
-  <si>
     <t>B0CKHVHVQ1</t>
   </si>
   <si>
@@ -213,15 +177,6 @@
     <t>BOM5</t>
   </si>
   <si>
-    <t>B0FQBTRM28</t>
-  </si>
-  <si>
-    <t>FBA79841</t>
-  </si>
-  <si>
-    <t>AH-60 BL</t>
-  </si>
-  <si>
     <t>B0D3M1B4Z8</t>
   </si>
   <si>
@@ -249,15 +204,6 @@
     <t>AI-10</t>
   </si>
   <si>
-    <t>B0BLJVJ2GN</t>
-  </si>
-  <si>
-    <t>FBA76414</t>
-  </si>
-  <si>
-    <t>AA-05</t>
-  </si>
-  <si>
     <t>B0B4DPX2J2</t>
   </si>
   <si>
@@ -267,15 +213,6 @@
     <t>AM-C1</t>
   </si>
   <si>
-    <t>B07WLWN2ZT</t>
-  </si>
-  <si>
-    <t>FBA77101</t>
-  </si>
-  <si>
-    <t>TC-777</t>
-  </si>
-  <si>
     <t>B0FQBXS6Y2</t>
   </si>
   <si>
@@ -432,15 +369,6 @@
     <t>FBA79845</t>
   </si>
   <si>
-    <t>B0GN97RFPR</t>
-  </si>
-  <si>
-    <t>FBA79848</t>
-  </si>
-  <si>
-    <t>AM-S2</t>
-  </si>
-  <si>
     <t>B0G53H49BS</t>
   </si>
   <si>
@@ -468,15 +396,6 @@
     <t>SB-01</t>
   </si>
   <si>
-    <t>B0DFMLXD9S</t>
-  </si>
-  <si>
-    <t>FBA79447</t>
-  </si>
-  <si>
-    <t>AM-W34</t>
-  </si>
-  <si>
     <t>B0CM9L1QZG</t>
   </si>
   <si>
@@ -495,12 +414,6 @@
     <t>AM-C10</t>
   </si>
   <si>
-    <t>B0FTVVLNS9</t>
-  </si>
-  <si>
-    <t>FBA79906</t>
-  </si>
-  <si>
     <t>B0BPLZ5CGV</t>
   </si>
   <si>
@@ -537,9 +450,6 @@
     <t>FBA80085</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>M6</t>
   </si>
   <si>
@@ -549,12 +459,6 @@
     <t>8UA61YIM_B0GXPBHDRF</t>
   </si>
   <si>
-    <t>8HS2F39O</t>
-  </si>
-  <si>
-    <t>8HS2F39O_B0GXPBHDRF</t>
-  </si>
-  <si>
     <t>3HUTGMNU</t>
   </si>
   <si>
@@ -606,24 +510,6 @@
     <t>AM-C28</t>
   </si>
   <si>
-    <t>B0FJ2J6MTF</t>
-  </si>
-  <si>
-    <t>FBA79822</t>
-  </si>
-  <si>
-    <t>5W7E44HK</t>
-  </si>
-  <si>
-    <t>5W7E44HK_B0G53H49BS</t>
-  </si>
-  <si>
-    <t>5W7E44HK_B0DT6T6N6B</t>
-  </si>
-  <si>
-    <t>BLR8</t>
-  </si>
-  <si>
     <t>B0CSCT63BL</t>
   </si>
   <si>
@@ -669,21 +555,6 @@
     <t>T30</t>
   </si>
   <si>
-    <t>5UZF5LAD</t>
-  </si>
-  <si>
-    <t>5UZF5LAD_B0GXPBHDRF</t>
-  </si>
-  <si>
-    <t>5UZF5LAD_B0GN97RFPR</t>
-  </si>
-  <si>
-    <t>5UZF5LAD_B0G53M9258</t>
-  </si>
-  <si>
-    <t>5UZF5LAD_B0CKHVHVQ1</t>
-  </si>
-  <si>
     <t>B0CF5SHL15</t>
   </si>
   <si>
@@ -693,27 +564,9 @@
     <t>AA-22</t>
   </si>
   <si>
-    <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
-  </si>
-  <si>
     <t>UB-02 (AM-S1 + AA-21)</t>
   </si>
   <si>
-    <t>KB-01 (AM-W32 + AI-12)</t>
-  </si>
-  <si>
-    <t>7YOH2NKK</t>
-  </si>
-  <si>
-    <t>7YOH2NKK_B0FTVVLNS9</t>
-  </si>
-  <si>
-    <t>7YOH2NKK_B0FN7B3KWS</t>
-  </si>
-  <si>
-    <t>7YOH2NKK_B0FJ2J6MTF</t>
-  </si>
-  <si>
     <t>B0G3B152FR</t>
   </si>
   <si>
@@ -723,24 +576,6 @@
     <t>AM-W47 Wireless</t>
   </si>
   <si>
-    <t>B0D3Q2T5XX</t>
-  </si>
-  <si>
-    <t>FBA79356</t>
-  </si>
-  <si>
-    <t>AA-19WL</t>
-  </si>
-  <si>
-    <t>B0D3LZWTHV</t>
-  </si>
-  <si>
-    <t>FBA79379</t>
-  </si>
-  <si>
-    <t>AM-C45</t>
-  </si>
-  <si>
     <t>B0CJR76Y7G</t>
   </si>
   <si>
@@ -768,30 +603,6 @@
     <t>AM-C11X</t>
   </si>
   <si>
-    <t>B0B4WTHLX5</t>
-  </si>
-  <si>
-    <t>FBA79574</t>
-  </si>
-  <si>
-    <t>TC30S</t>
-  </si>
-  <si>
-    <t>B0B4DS678Q</t>
-  </si>
-  <si>
-    <t>FBA75676</t>
-  </si>
-  <si>
-    <t>AM-C4</t>
-  </si>
-  <si>
-    <t>7FQYAOFK</t>
-  </si>
-  <si>
-    <t>7FQYAOFK_B0DXFPM4N2</t>
-  </si>
-  <si>
     <t>6YGKNZUA</t>
   </si>
   <si>
@@ -816,9 +627,6 @@
     <t>83J17WIT_B0CM6WH4ZT</t>
   </si>
   <si>
-    <t>2CD9LHMV</t>
-  </si>
-  <si>
     <t>B0GN2LHJY4</t>
   </si>
   <si>
@@ -828,9 +636,6 @@
     <t>MT-12</t>
   </si>
   <si>
-    <t>2CD9LHMV_B0CKHVHVQ1</t>
-  </si>
-  <si>
     <t>B0B4G5ZLTB</t>
   </si>
   <si>
@@ -840,27 +645,6 @@
     <t>AM-W11</t>
   </si>
   <si>
-    <t>4DSOJAGY</t>
-  </si>
-  <si>
-    <t>4DSOJAGY_B0GN2LHJY4</t>
-  </si>
-  <si>
-    <t>4DSOJAGY_B0GCP1J2HC</t>
-  </si>
-  <si>
-    <t>4DSOJAGY_B0G4DNF8RZ</t>
-  </si>
-  <si>
-    <t>4DSOJAGY_B0CF5SHL15</t>
-  </si>
-  <si>
-    <t>4DSOJAGY_B0CF5R3V95</t>
-  </si>
-  <si>
-    <t>4DSOJAGY_B0B4DPX2J2</t>
-  </si>
-  <si>
     <t>2H5JO5ZI</t>
   </si>
   <si>
@@ -906,18 +690,6 @@
     <t>1RRJCKOC_B089FVQD3Z</t>
   </si>
   <si>
-    <t>8FS31JAC</t>
-  </si>
-  <si>
-    <t>8FS31JAC_B0G3B152FR</t>
-  </si>
-  <si>
-    <t>8FS31JAC_B0CKHVHVQ1</t>
-  </si>
-  <si>
-    <t>8FS31JAC_B0BLJVJ2GN</t>
-  </si>
-  <si>
     <t>1DOX52VO</t>
   </si>
   <si>
@@ -939,12 +711,6 @@
     <t>4CZ8R7OL_B0DXFPM4N2</t>
   </si>
   <si>
-    <t>73T76NEC</t>
-  </si>
-  <si>
-    <t>73T76NEC_B0CF5TCQKL</t>
-  </si>
-  <si>
     <t>B0CF5TCQKL</t>
   </si>
   <si>
@@ -954,18 +720,6 @@
     <t>AA-21</t>
   </si>
   <si>
-    <t>8XOORSPA</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0GXPBHDRF</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0GN2LHJY4</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0G39ZHDYP</t>
-  </si>
-  <si>
     <t>B0G39ZHDYP</t>
   </si>
   <si>
@@ -975,33 +729,6 @@
     <t>AM-W47 Wired</t>
   </si>
   <si>
-    <t>8XOORSPA_B0FQBXS6Y2</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0FQBTRM28</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0FG88HVQ8</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0DT6T6N6B</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0DFMLXD9S</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0D3Q2T5XX</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0D3M1B4Z8</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0D3LZWTHV</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CQX4K9P5</t>
-  </si>
-  <si>
     <t>B0CQX4K9P5</t>
   </si>
   <si>
@@ -1011,87 +738,6 @@
     <t>TD310</t>
   </si>
   <si>
-    <t>8XOORSPA_B0CM9L1QZG</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CM6WH4ZT</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CM6NVLT9</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CM6NTWBP</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CJR76Y7G</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CH4VCD6R</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CH4RNWJX</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CF5SHL15</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CF5R3V95</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CBCB82MT</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0CBC7QMNV</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0C4YSV3XL</t>
-  </si>
-  <si>
-    <t>B0C4YSV3XL</t>
-  </si>
-  <si>
-    <t>FBA78206</t>
-  </si>
-  <si>
-    <t>AM-W15</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0BYHHSLPC</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0BPLZ5CGV</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4WTHLX5</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4KC7VBM</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4K87PR4</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4JRQP22</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4G94VP3</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4G8PH2P</t>
-  </si>
-  <si>
-    <t>B0B4G8PH2P</t>
-  </si>
-  <si>
-    <t>FBA75678</t>
-  </si>
-  <si>
-    <t>AA-01</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4G7VWXD</t>
-  </si>
-  <si>
     <t>B0B4G7VWXD</t>
   </si>
   <si>
@@ -1101,15 +747,6 @@
     <t>AA-04</t>
   </si>
   <si>
-    <t>8XOORSPA_B0B4G763WS</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4G5ZLTB</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4G5JG4P</t>
-  </si>
-  <si>
     <t>B0B4G5JG4P</t>
   </si>
   <si>
@@ -1119,21 +756,6 @@
     <t>AM-W14</t>
   </si>
   <si>
-    <t>8XOORSPA_B0B4G19R58</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4DS678Q</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B0B4DPX2J2</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B07WLWN2ZT</t>
-  </si>
-  <si>
-    <t>8XOORSPA_B01ISNU3X4</t>
-  </si>
-  <si>
     <t>25KOAIGF</t>
   </si>
   <si>
@@ -1264,6 +886,168 @@
   </si>
   <si>
     <t>78MQ6L1R_B0GN8MPYPG</t>
+  </si>
+  <si>
+    <t>6A3J5LUT</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0GXP97CZG</t>
+  </si>
+  <si>
+    <t>B0GXP97CZG</t>
+  </si>
+  <si>
+    <t>FBA80084</t>
+  </si>
+  <si>
+    <t>BE-4</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0GN2LHJY4</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0G3B152FR</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0G39ZHDYP</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0FQJWWDVK</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0FQBXS6Y2</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0D3M86SH1</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0D3M1B4Z8</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CSCT63BL</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CM9L1QZG</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CM6NVLT9</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CM6NTWBP</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CKHVHVQ1</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CJR76Y7G</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CH4VCD6R</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CH4RNWJX</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CFKHCQ8W</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CF5SHL15</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CF5R3V95</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CCV74CL7</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0CBCB82MT</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>FBA79113</t>
+  </si>
+  <si>
+    <t>TC310</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0BPLZ5CGV</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0B4KC7VBM</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0B4K87PR4</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0B4G94VP3</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0B4G19R58</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B0B4DPX2J2</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B08CVP2HXP</t>
+  </si>
+  <si>
+    <t>6A3J5LUT_B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>64YX15GS</t>
+  </si>
+  <si>
+    <t>64YX15GS_B0CF5TCQKL</t>
+  </si>
+  <si>
+    <t>4BBA1LRU</t>
+  </si>
+  <si>
+    <t>4BBA1LRU_B0B4K87PR4</t>
+  </si>
+  <si>
+    <t>5OX83Z1Y</t>
+  </si>
+  <si>
+    <t>5OX83Z1Y_B0GN8MMKY1</t>
+  </si>
+  <si>
+    <t>B0GN8MMKY1</t>
+  </si>
+  <si>
+    <t>FBA79980</t>
+  </si>
+  <si>
+    <t>AK-37-W</t>
+  </si>
+  <si>
+    <t>5OX83Z1Y_B0FG88HVQ8</t>
+  </si>
+  <si>
+    <t>5OX83Z1Y_B0CM6NVLT9</t>
+  </si>
+  <si>
+    <t>8X4APETR</t>
+  </si>
+  <si>
+    <t>8X4APETR_B0FQBXS6Y2</t>
+  </si>
+  <si>
+    <t>8X4APETR_B0CM6NTWBP</t>
+  </si>
+  <si>
+    <t>6CPAHDWO</t>
+  </si>
+  <si>
+    <t>6CPAHDWO_B0G3B152FR</t>
+  </si>
+  <si>
+    <t>6CPAHDWO_B0CH4VCD6R</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1361,7 +1145,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1369,9 +1152,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -22172,7 +21952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5A3FE4-F9D3-480E-B305-3F537BEA10CA}">
-  <dimension ref="A1:P122"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.296875" bestFit="1" customWidth="1"/>
@@ -22245,10 +22025,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>16</v>
@@ -22257,20 +22037,20 @@
         <v>46132</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>262700615</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>176</v>
+        <v>41</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="K2" s="4">
         <v>5</v>
@@ -22293,10 +22073,10 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
@@ -22305,20 +22085,20 @@
         <v>46132</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>262700615</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>177</v>
+        <v>32</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K3" s="4">
         <v>3</v>
@@ -22341,10 +22121,10 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>16</v>
@@ -22353,20 +22133,20 @@
         <v>46132</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>262700615</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>178</v>
+        <v>73</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -22389,10 +22169,10 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>16</v>
@@ -22401,20 +22181,20 @@
         <v>46132</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>262700615</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>179</v>
+        <v>90</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -22437,10 +22217,10 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>16</v>
@@ -22449,20 +22229,20 @@
         <v>46132</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>262700615</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>175</v>
+        <v>82</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="K6" s="4">
         <v>3</v>
@@ -22485,10 +22265,10 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>16</v>
@@ -22497,20 +22277,20 @@
         <v>46132</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>262700615</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>181</v>
+        <v>70</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="K7" s="4">
         <v>4</v>
@@ -22533,10 +22313,10 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>16</v>
@@ -22545,20 +22325,20 @@
         <v>46132</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>262700615</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>175</v>
+        <v>79</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="K8" s="4">
         <v>3</v>
@@ -22580,31 +22360,33 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>168</v>
+      <c r="A9" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D9" s="5">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="7">
-        <v>262701728</v>
+      <c r="F9" s="6">
+        <v>262701736</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I9" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="J9" s="4" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="K9" s="4">
         <v>7</v>
@@ -22615,203 +22397,205 @@
       <c r="M9" s="3">
         <v>0</v>
       </c>
-      <c r="N9" s="4">
-        <v>5242.94</v>
-      </c>
-      <c r="O9" s="4">
-        <v>36700.579999999994</v>
+      <c r="N9" s="8">
+        <v>1023.0889830508474</v>
+      </c>
+      <c r="O9" s="8">
+        <v>7161.6228813559319</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>170</v>
+      <c r="A10" s="4" t="s">
+        <v>217</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D10" s="5">
-        <v>46174</v>
+        <v>46206</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="7">
-        <v>262701731</v>
-      </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>166</v>
+        <v>154</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="K10" s="4">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="L10" s="4">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>5242.94</v>
+        <v>1219.45</v>
       </c>
       <c r="O10" s="4">
-        <v>10485.88</v>
+        <v>243890</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>172</v>
+      <c r="A11" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D11" s="5">
-        <v>46174</v>
+        <v>46209</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="7">
-        <v>262701293</v>
+      <c r="F11" s="6">
+        <v>262701727</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I11" s="7">
-        <v>85437022</v>
+        <v>64</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="K11" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M11" s="3">
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>5242.94</v>
+        <v>7340.4</v>
       </c>
       <c r="O11" s="4">
-        <v>20971.759999999998</v>
+        <v>14680.8</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>191</v>
+      <c r="A12" s="4" t="s">
+        <v>246</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D12" s="5">
-        <v>46181</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7">
-        <v>262701733</v>
+        <v>46209</v>
+      </c>
+      <c r="E12" s="9">
+        <v>46214</v>
+      </c>
+      <c r="F12" s="6">
+        <v>262701725</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>177</v>
+        <v>113</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="K12" s="4">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L12" s="4">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>2020.51</v>
+        <v>348.94</v>
       </c>
       <c r="O12" s="4">
-        <v>48492.24</v>
+        <v>697.88</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>191</v>
+      <c r="A13" s="4" t="s">
+        <v>246</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5">
-        <v>46181</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7">
-        <v>262701733</v>
+        <v>46209</v>
+      </c>
+      <c r="E13" s="9">
+        <v>46214</v>
+      </c>
+      <c r="F13" s="6">
+        <v>262701725</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>178</v>
+        <v>185</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="K13" s="4">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L13" s="4">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>412.5</v>
+        <v>2726</v>
       </c>
       <c r="O13" s="4">
-        <v>8662.5</v>
+        <v>2726</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>18</v>
@@ -22819,47 +22603,49 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="C14" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D14" s="5">
-        <v>46195</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7">
-        <v>262701735</v>
+        <v>46209</v>
+      </c>
+      <c r="E14" s="9">
+        <v>46214</v>
+      </c>
+      <c r="F14" s="6">
+        <v>262701725</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>182</v>
+        <v>199</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="K14" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L14" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="9">
-        <v>7340.4025423728808</v>
-      </c>
-      <c r="O14" s="9">
-        <v>88084.830508474566</v>
+      <c r="N14" s="4">
+        <v>1885.77</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1885.77</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>18</v>
@@ -22867,47 +22653,47 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5">
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="7">
-        <v>262701738</v>
+      <c r="F15" s="6">
+        <v>262701852</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>177</v>
+        <v>122</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="K15" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="9">
-        <v>6641.2500000000009</v>
-      </c>
-      <c r="O15" s="9">
-        <v>19923.750000000004</v>
+      <c r="N15" s="4">
+        <v>2900.78</v>
+      </c>
+      <c r="O15" s="4">
+        <v>5801.56</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>18</v>
@@ -22915,47 +22701,47 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D16" s="5">
-        <v>46195</v>
+        <v>46216</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="7">
-        <v>262701738</v>
+      <c r="F16" s="6">
+        <v>262701852</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>177</v>
+        <v>28</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K16" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L16" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M16" s="3">
         <v>0</v>
       </c>
-      <c r="N16" s="9">
-        <v>8389.1313559322025</v>
-      </c>
-      <c r="O16" s="9">
-        <v>75502.182203389821</v>
+      <c r="N16" s="4">
+        <v>2121.5700000000002</v>
+      </c>
+      <c r="O16" s="4">
+        <v>2121.5700000000002</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>18</v>
@@ -22963,47 +22749,47 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="E17" s="6"/>
-      <c r="F17" s="7">
-        <v>262701738</v>
+      <c r="F17" s="6">
+        <v>262701847</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>179</v>
+        <v>41</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>255</v>
+        <v>43</v>
       </c>
       <c r="K17" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L17" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9">
-        <v>10137.012711864407</v>
-      </c>
-      <c r="O17" s="9">
-        <v>20274.025423728814</v>
+        <v>5</v>
+      </c>
+      <c r="N17" s="4">
+        <v>4054.39</v>
+      </c>
+      <c r="O17" s="4">
+        <v>36489.51</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>18</v>
@@ -23011,320 +22797,306 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D18" s="5">
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="E18" s="6"/>
-      <c r="F18" s="7">
-        <v>262701738</v>
-      </c>
+      <c r="F18" s="6"/>
       <c r="G18" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>181</v>
+        <v>285</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>93</v>
+        <v>287</v>
       </c>
       <c r="K18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
-      <c r="N18" s="9">
-        <v>1023.0889830508474</v>
-      </c>
-      <c r="O18" s="9">
-        <v>1023.0889830508474</v>
+      <c r="N18" s="4">
+        <v>3145.49</v>
+      </c>
+      <c r="O18" s="4">
+        <v>6290.98</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5">
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="E19" s="6"/>
-      <c r="F19" s="7">
-        <v>262701736</v>
-      </c>
+      <c r="F19" s="6"/>
       <c r="G19" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>181</v>
+        <v>196</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="K19" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M19" s="3">
         <v>0</v>
       </c>
-      <c r="N19" s="9">
-        <v>1023.0889830508474</v>
-      </c>
-      <c r="O19" s="9">
-        <v>7161.6228813559319</v>
+      <c r="N19" s="4">
+        <v>6851</v>
+      </c>
+      <c r="O19" s="4">
+        <v>34255</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D20" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E20" s="6"/>
-      <c r="F20" s="7">
-        <v>262701688</v>
-      </c>
+      <c r="F20" s="6"/>
       <c r="G20" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>183</v>
+        <v>176</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>262</v>
+        <v>178</v>
       </c>
       <c r="K20" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="9">
-        <v>6851</v>
-      </c>
-      <c r="O20" s="9">
-        <v>6851</v>
+      <c r="N20" s="4">
+        <v>1548.9</v>
+      </c>
+      <c r="O20" s="4">
+        <v>4646.7000000000007</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E21" s="6"/>
-      <c r="F21" s="7">
-        <v>262701688</v>
-      </c>
+      <c r="F21" s="6"/>
       <c r="G21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>181</v>
+        <v>227</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="K21" s="4">
-        <v>58</v>
-      </c>
-      <c r="L21" s="10">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="L21" s="4">
+        <v>5</v>
       </c>
       <c r="M21" s="3">
-        <v>38</v>
-      </c>
-      <c r="N21" s="9">
-        <v>6151.8432203389839</v>
-      </c>
-      <c r="O21" s="9">
-        <v>356806.90677966108</v>
+        <v>0</v>
+      </c>
+      <c r="N21" s="4">
+        <v>959.11</v>
+      </c>
+      <c r="O21" s="4">
+        <v>4795.55</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D22" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E22" s="6"/>
-      <c r="F22" s="7">
-        <v>262701688</v>
-      </c>
+      <c r="F22" s="6"/>
       <c r="G22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>178</v>
+        <v>113</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="K22" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L22" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="9">
-        <v>2586.17</v>
-      </c>
-      <c r="O22" s="9">
-        <v>12930.85</v>
+      <c r="N22" s="4">
+        <v>348.94</v>
+      </c>
+      <c r="O22" s="4">
+        <v>348.94</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D23" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="7">
-        <v>262701688</v>
-      </c>
+      <c r="F23" s="6"/>
       <c r="G23" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>182</v>
+        <v>58</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>217</v>
+        <v>60</v>
       </c>
       <c r="K23" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L23" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
       </c>
-      <c r="N23" s="9">
-        <v>2541.7399999999998</v>
-      </c>
-      <c r="O23" s="9">
-        <v>5083.4799999999996</v>
+      <c r="N23" s="4">
+        <v>1119.06</v>
+      </c>
+      <c r="O23" s="4">
+        <v>12309.66</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E24" s="6"/>
-      <c r="F24" s="7">
-        <v>262701688</v>
-      </c>
+      <c r="F24" s="6"/>
       <c r="G24" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>178</v>
+        <v>67</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="K24" s="4">
         <v>2</v>
@@ -23335,92 +23107,88 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="9">
-        <v>2668.86</v>
-      </c>
-      <c r="O24" s="9">
-        <v>5337.72</v>
+      <c r="N24" s="4">
+        <v>3304.45</v>
+      </c>
+      <c r="O24" s="4">
+        <v>6608.9</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D25" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="7">
-        <v>262701688</v>
-      </c>
+      <c r="F25" s="6"/>
       <c r="G25" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>175</v>
+        <v>46</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="9">
-        <v>1919.45</v>
-      </c>
-      <c r="O25" s="9">
-        <v>3838.9</v>
+      <c r="N25" s="4">
+        <v>2656.08</v>
+      </c>
+      <c r="O25" s="4">
+        <v>2656.08</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D26" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E26" s="6"/>
-      <c r="F26" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F26" s="6"/>
       <c r="G26" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>183</v>
+        <v>157</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -23431,428 +23199,410 @@
       <c r="M26" s="3">
         <v>0</v>
       </c>
-      <c r="N26" s="9">
-        <v>6851</v>
-      </c>
-      <c r="O26" s="9">
-        <v>6851</v>
+      <c r="N26" s="4">
+        <v>1751.02</v>
+      </c>
+      <c r="O26" s="4">
+        <v>1751.02</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D27" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E27" s="6"/>
-      <c r="F27" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F27" s="6"/>
       <c r="G27" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>177</v>
+        <v>119</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="K27" s="4">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L27" s="4">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
-      <c r="N27" s="9">
-        <v>8389.1299999999992</v>
-      </c>
-      <c r="O27" s="9">
-        <v>285230.42</v>
+      <c r="N27" s="4">
+        <v>959.11</v>
+      </c>
+      <c r="O27" s="4">
+        <v>959.11</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D28" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="F28" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F28" s="6"/>
       <c r="G28" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>177</v>
+        <v>49</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="K28" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L28" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="9">
-        <v>2155.2600000000002</v>
-      </c>
-      <c r="O28" s="9">
-        <v>23707.86</v>
+      <c r="N28" s="4">
+        <v>1119.06</v>
+      </c>
+      <c r="O28" s="4">
+        <v>1119.06</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D29" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="6"/>
-      <c r="F29" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F29" s="6"/>
       <c r="G29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>179</v>
+        <v>52</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>255</v>
+        <v>54</v>
       </c>
       <c r="K29" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="9">
-        <v>10137.01</v>
-      </c>
-      <c r="O29" s="9">
-        <v>20274.02</v>
+      <c r="N29" s="4">
+        <v>2460.3200000000002</v>
+      </c>
+      <c r="O29" s="4">
+        <v>7380.9600000000009</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D30" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E30" s="6"/>
-      <c r="F30" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F30" s="6"/>
       <c r="G30" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>185</v>
+        <v>38</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="K30" s="4">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="L30" s="4">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="9">
-        <v>1548.9</v>
-      </c>
-      <c r="O30" s="9">
-        <v>4646.7000000000007</v>
+      <c r="N30" s="4">
+        <v>3844.64</v>
+      </c>
+      <c r="O30" s="4">
+        <v>130717.75999999999</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D31" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="F31" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F31" s="6"/>
       <c r="G31" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I31" s="7" t="s">
         <v>179</v>
       </c>
+      <c r="H31" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="J31" s="4" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="K31" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L31" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="9">
-        <v>10137.01</v>
-      </c>
-      <c r="O31" s="9">
-        <v>40548.04</v>
+      <c r="N31" s="4">
+        <v>571.4</v>
+      </c>
+      <c r="O31" s="4">
+        <v>1142.8</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D32" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F32" s="6"/>
       <c r="G32" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>183</v>
+        <v>128</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K32" s="4">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="L32" s="4">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="9">
-        <v>959.11</v>
-      </c>
-      <c r="O32" s="9">
-        <v>8631.99</v>
+      <c r="N32" s="4">
+        <v>412.5</v>
+      </c>
+      <c r="O32" s="4">
+        <v>19800</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D33" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F33" s="6"/>
       <c r="G33" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>175</v>
+        <v>99</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="K33" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
       </c>
-      <c r="N33" s="9">
-        <v>1461.23</v>
-      </c>
-      <c r="O33" s="9">
-        <v>1461.23</v>
+      <c r="N33" s="4">
+        <v>1818.39</v>
+      </c>
+      <c r="O33" s="4">
+        <v>5455.17</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D34" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F34" s="6"/>
       <c r="G34" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>182</v>
+        <v>102</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>217</v>
+        <v>104</v>
       </c>
       <c r="K34" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="9">
-        <v>2541.7399999999998</v>
-      </c>
-      <c r="O34" s="9">
-        <v>5083.4799999999996</v>
+      <c r="N34" s="4">
+        <v>1461.23</v>
+      </c>
+      <c r="O34" s="4">
+        <v>4383.6900000000005</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D35" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E35" s="6"/>
-      <c r="F35" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F35" s="6"/>
       <c r="G35" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="K35" s="4">
         <v>2</v>
@@ -23863,92 +23613,88 @@
       <c r="M35" s="3">
         <v>0</v>
       </c>
-      <c r="N35" s="9">
-        <v>1524.79</v>
-      </c>
-      <c r="O35" s="9">
-        <v>3049.58</v>
+      <c r="N35" s="4">
+        <v>2541.7399999999998</v>
+      </c>
+      <c r="O35" s="4">
+        <v>5083.4799999999996</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D36" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="F36" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F36" s="6"/>
       <c r="G36" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>175</v>
+        <v>131</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
       </c>
-      <c r="N36" s="9">
-        <v>2020.51</v>
-      </c>
-      <c r="O36" s="9">
-        <v>4041.02</v>
+      <c r="N36" s="4">
+        <v>2668.86</v>
+      </c>
+      <c r="O36" s="4">
+        <v>2668.86</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D37" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E37" s="6"/>
-      <c r="F37" s="7">
-        <v>262701686</v>
-      </c>
+      <c r="F37" s="6"/>
       <c r="G37" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>175</v>
+        <v>76</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K37" s="4">
         <v>1</v>
@@ -23959,474 +23705,456 @@
       <c r="M37" s="3">
         <v>0</v>
       </c>
-      <c r="N37" s="9">
-        <v>2935.74</v>
-      </c>
-      <c r="O37" s="9">
-        <v>2935.74</v>
+      <c r="N37" s="4">
+        <v>2020.51</v>
+      </c>
+      <c r="O37" s="4">
+        <v>2020.51</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D38" s="5">
-        <v>46202</v>
+        <v>46223</v>
       </c>
       <c r="E38" s="6"/>
-      <c r="F38" s="7">
-        <v>262701687</v>
-      </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>182</v>
+        <v>22</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>209</v>
+        <v>24</v>
       </c>
       <c r="K38" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L38" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
       </c>
-      <c r="N38" s="9">
-        <v>1906.14</v>
-      </c>
-      <c r="O38" s="9">
-        <v>7624.56</v>
+      <c r="N38" s="4">
+        <v>1245.72</v>
+      </c>
+      <c r="O38" s="4">
+        <v>1245.72</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D39" s="5">
-        <v>46206</v>
+        <v>46223</v>
       </c>
       <c r="E39" s="6"/>
-      <c r="F39" s="7"/>
+      <c r="F39" s="6"/>
       <c r="G39" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>174</v>
+        <v>309</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>188</v>
+        <v>311</v>
       </c>
       <c r="K39" s="4">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="L39" s="4">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="M39" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N39" s="4">
-        <v>1219.45</v>
+        <v>1751.02</v>
       </c>
       <c r="O39" s="4">
-        <v>243890</v>
+        <v>14008.16</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D40" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E40" s="6"/>
-      <c r="F40" s="7">
-        <v>262701739</v>
-      </c>
+      <c r="F40" s="6"/>
       <c r="G40" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>182</v>
+        <v>125</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K40" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L40" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M40" s="3">
         <v>0</v>
       </c>
       <c r="N40" s="4">
-        <v>7340.4</v>
+        <v>3704.81</v>
       </c>
       <c r="O40" s="4">
-        <v>190850.4</v>
+        <v>100029.87</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D41" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E41" s="6"/>
-      <c r="F41" s="7">
-        <v>262701739</v>
-      </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="K41" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L41" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
       <c r="N41" s="4">
-        <v>1906.14</v>
+        <v>1751.02</v>
       </c>
       <c r="O41" s="4">
-        <v>3812.28</v>
+        <v>12257.14</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D42" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E42" s="6"/>
-      <c r="F42" s="7">
-        <v>262701727</v>
-      </c>
+      <c r="F42" s="6"/>
       <c r="G42" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>182</v>
+        <v>122</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="K42" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
       <c r="N42" s="4">
-        <v>7340.4</v>
+        <v>2900.78</v>
       </c>
       <c r="O42" s="4">
-        <v>14680.8</v>
+        <v>2900.78</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D43" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E43" s="6"/>
-      <c r="F43" s="7">
-        <v>262701740</v>
-      </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>180</v>
+        <v>25</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="K43" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L43" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
       <c r="N43" s="4">
-        <v>1119.06</v>
+        <v>348.94</v>
       </c>
       <c r="O43" s="4">
-        <v>12309.66</v>
+        <v>4536.22</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D44" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E44" s="6"/>
-      <c r="F44" s="7">
-        <v>262701740</v>
-      </c>
+      <c r="F44" s="6"/>
       <c r="G44" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>174</v>
+        <v>61</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>323</v>
+        <v>63</v>
       </c>
       <c r="K44" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L44" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="9">
-        <v>1397.6694915254238</v>
+      <c r="N44" s="4">
+        <v>2935.74</v>
       </c>
       <c r="O44" s="4">
-        <v>9783.6864406779678</v>
+        <v>2935.74</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D45" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E45" s="6"/>
-      <c r="F45" s="7">
-        <v>262701740</v>
-      </c>
+      <c r="F45" s="6"/>
       <c r="G45" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>175</v>
+        <v>55</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="K45" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L45" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
       <c r="N45" s="4">
-        <v>571.4</v>
+        <v>1919.45</v>
       </c>
       <c r="O45" s="4">
-        <v>571.4</v>
+        <v>19194.5</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>369</v>
+        <v>318</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D46" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E46" s="6"/>
-      <c r="F46" s="7">
-        <v>262701740</v>
-      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>178</v>
+        <v>264</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>159</v>
+        <v>266</v>
       </c>
       <c r="K46" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L46" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
       <c r="N46" s="4">
-        <v>412.5</v>
+        <v>1616.28</v>
       </c>
       <c r="O46" s="4">
-        <v>2475</v>
+        <v>3232.56</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>370</v>
+        <v>319</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D47" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E47" s="6"/>
-      <c r="F47" s="7">
-        <v>262701740</v>
-      </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>182</v>
+        <v>160</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="K47" s="4">
         <v>5</v>
@@ -24438,187 +24166,179 @@
         <v>0</v>
       </c>
       <c r="N47" s="4">
-        <v>1715.47</v>
+        <v>1346.78</v>
       </c>
       <c r="O47" s="4">
-        <v>8577.35</v>
+        <v>6733.9</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>371</v>
+        <v>321</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D48" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="7">
-        <v>262701740</v>
-      </c>
+      <c r="F48" s="6"/>
       <c r="G48" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>174</v>
+        <v>224</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>353</v>
+        <v>226</v>
       </c>
       <c r="K48" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L48" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
       <c r="N48" s="4">
-        <v>1133.9000000000001</v>
+        <v>2541.7399999999998</v>
       </c>
       <c r="O48" s="4">
-        <v>5669.5</v>
+        <v>5083.4799999999996</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>372</v>
+        <v>322</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>373</v>
+        <v>323</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D49" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="7">
-        <v>262701725</v>
-      </c>
+      <c r="F49" s="6"/>
       <c r="G49" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>182</v>
+        <v>122</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="K49" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L49" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
       <c r="N49" s="4">
-        <v>348.94</v>
+        <v>2900.78</v>
       </c>
       <c r="O49" s="4">
-        <v>697.88</v>
+        <v>8702.34</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>374</v>
+        <v>325</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D50" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="7">
-        <v>262701725</v>
-      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>178</v>
+        <v>326</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>242</v>
+        <v>328</v>
       </c>
       <c r="K50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" s="3">
         <v>0</v>
       </c>
       <c r="N50" s="4">
-        <v>2726</v>
+        <v>3005.66</v>
       </c>
       <c r="O50" s="4">
-        <v>2726</v>
+        <v>6011.32</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D51" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E51" s="6"/>
-      <c r="F51" s="7">
-        <v>262701725</v>
-      </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>175</v>
+        <v>19</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="K51" s="4">
         <v>1</v>
@@ -24630,135 +24350,133 @@
         <v>0</v>
       </c>
       <c r="N51" s="4">
-        <v>1885.77</v>
+        <v>1481.53</v>
       </c>
       <c r="O51" s="4">
-        <v>1885.77</v>
+        <v>1481.53</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>377</v>
+        <v>330</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D52" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="7">
-        <v>262701729</v>
-      </c>
+      <c r="F52" s="6"/>
       <c r="G52" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>174</v>
+        <v>49</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>323</v>
+        <v>51</v>
       </c>
       <c r="K52" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L52" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="9">
-        <v>1397.6694915254238</v>
+      <c r="N52" s="4">
+        <v>1119.06</v>
       </c>
       <c r="O52" s="4">
-        <v>4193.0084745762715</v>
+        <v>6714.36</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>378</v>
+        <v>331</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D53" s="5">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="E53" s="6"/>
-      <c r="F53" s="7"/>
+      <c r="F53" s="6"/>
       <c r="G53" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>184</v>
+        <v>58</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="K53" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
       </c>
       <c r="N53" s="4">
-        <v>3304.45</v>
+        <v>1119.06</v>
       </c>
       <c r="O53" s="4">
-        <v>3304.45</v>
+        <v>3357.18</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>378</v>
+        <v>331</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>380</v>
+        <v>333</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D54" s="5">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="E54" s="6"/>
-      <c r="F54" s="7"/>
+      <c r="F54" s="6"/>
       <c r="G54" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>175</v>
+        <v>52</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="K54" s="4">
         <v>1</v>
@@ -24770,363 +24488,385 @@
         <v>0</v>
       </c>
       <c r="N54" s="4">
-        <v>1751.02</v>
+        <v>2460.3200000000002</v>
       </c>
       <c r="O54" s="4">
-        <v>1751.02</v>
+        <v>2460.3200000000002</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D55" s="5">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="E55" s="6"/>
-      <c r="F55" s="7"/>
+      <c r="F55" s="6"/>
       <c r="G55" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="K55" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
       </c>
       <c r="N55" s="4">
-        <v>571.4</v>
+        <v>1548.9</v>
       </c>
       <c r="O55" s="4">
-        <v>1142.8</v>
+        <v>1548.9</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D56" s="5">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="E56" s="6"/>
-      <c r="F56" s="7"/>
+      <c r="F56" s="6"/>
       <c r="G56" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>182</v>
+        <v>128</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="K56" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L56" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M56" s="3">
         <v>0</v>
       </c>
       <c r="N56" s="4">
-        <v>2541.7399999999998</v>
+        <v>412.5</v>
       </c>
       <c r="O56" s="4">
-        <v>5083.4799999999996</v>
+        <v>2062.5</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>378</v>
+      <c r="A57" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>383</v>
+        <v>139</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D57" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="7"/>
+        <v>46174</v>
+      </c>
+      <c r="E57" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F57" s="6">
+        <v>262701728</v>
+      </c>
       <c r="G57" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>178</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I57" s="6"/>
       <c r="J57" s="4" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="K57" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L57" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
       <c r="N57" s="4">
-        <v>2668.86</v>
+        <v>5242.94</v>
       </c>
       <c r="O57" s="4">
-        <v>2668.86</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>163</v>
+        <v>36700.579999999994</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>378</v>
+      <c r="A58" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>384</v>
+        <v>141</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D58" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="7"/>
+        <v>46174</v>
+      </c>
+      <c r="E58" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F58" s="6">
+        <v>262701293</v>
+      </c>
       <c r="G58" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>175</v>
+        <v>135</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I58" s="6">
+        <v>85437022</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>206</v>
+        <v>137</v>
       </c>
       <c r="K58" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L58" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="4">
-        <v>1626.38</v>
+        <v>5242.94</v>
       </c>
       <c r="O58" s="4">
-        <v>1626.38</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>163</v>
+        <v>20971.759999999998</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>378</v>
+        <v>188</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>385</v>
+        <v>189</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D59" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="7"/>
+        <v>46195</v>
+      </c>
+      <c r="E59" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F59" s="6">
+        <v>262701738</v>
+      </c>
       <c r="G59" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>174</v>
+        <v>163</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K59" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L59" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
       </c>
       <c r="N59" s="4">
-        <v>2900.78</v>
+        <v>6641.2500000000009</v>
       </c>
       <c r="O59" s="4">
-        <v>2900.78</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>163</v>
+        <v>19923.750000000004</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>378</v>
+        <v>188</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>386</v>
+        <v>190</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D60" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="7"/>
+        <v>46195</v>
+      </c>
+      <c r="E60" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F60" s="6">
+        <v>262701738</v>
+      </c>
       <c r="G60" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H60" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I60" s="7" t="s">
-        <v>184</v>
+      <c r="H60" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K60" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L60" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
       <c r="N60" s="4">
-        <v>348.94</v>
+        <v>8389.1313559322025</v>
       </c>
       <c r="O60" s="4">
-        <v>348.94</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>163</v>
+        <v>75502.182203389821</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>378</v>
+        <v>188</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>387</v>
+        <v>191</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D61" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="7"/>
+        <v>46195</v>
+      </c>
+      <c r="E61" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F61" s="6">
+        <v>262701738</v>
+      </c>
       <c r="G61" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>174</v>
+        <v>90</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="K61" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="4">
-        <v>2935.74</v>
+        <v>10137.012711864407</v>
       </c>
       <c r="O61" s="4">
-        <v>2935.74</v>
-      </c>
-      <c r="P61" s="3" t="s">
-        <v>163</v>
+        <v>20274.025423728814</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>378</v>
+        <v>188</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>388</v>
+        <v>193</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D62" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="7"/>
+        <v>46195</v>
+      </c>
+      <c r="E62" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F62" s="6">
+        <v>262701738</v>
+      </c>
       <c r="G62" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="I62" s="7" t="s">
-        <v>175</v>
+        <v>70</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="K62" s="4">
         <v>1</v>
@@ -25138,41 +24878,45 @@
         <v>0</v>
       </c>
       <c r="N62" s="4">
-        <v>4683.62</v>
+        <v>1023.0889830508474</v>
       </c>
       <c r="O62" s="4">
-        <v>4683.62</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>163</v>
+        <v>1023.0889830508474</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>378</v>
+        <v>202</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D63" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E63" s="6"/>
-      <c r="F63" s="7"/>
+        <v>46202</v>
+      </c>
+      <c r="E63" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F63" s="6">
+        <v>262701686</v>
+      </c>
       <c r="G63" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>175</v>
+        <v>196</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>392</v>
+        <v>198</v>
       </c>
       <c r="K63" s="4">
         <v>1</v>
@@ -25184,133 +24928,145 @@
         <v>0</v>
       </c>
       <c r="N63" s="4">
-        <v>1616.28</v>
+        <v>6851</v>
       </c>
       <c r="O63" s="4">
-        <v>1616.28</v>
-      </c>
-      <c r="P63" s="3" t="s">
-        <v>163</v>
+        <v>6851</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>393</v>
+        <v>202</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>394</v>
+        <v>204</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D64" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="7"/>
+        <v>46202</v>
+      </c>
+      <c r="E64" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F64" s="6">
+        <v>262701686</v>
+      </c>
       <c r="G64" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>174</v>
+        <v>32</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="K64" s="4">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="L64" s="4">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="M64" s="3">
         <v>0</v>
       </c>
       <c r="N64" s="4">
-        <v>2900.78</v>
+        <v>8389.1299999999992</v>
       </c>
       <c r="O64" s="4">
-        <v>5801.56</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>163</v>
+        <v>285230.42</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>393</v>
+        <v>202</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>395</v>
+        <v>205</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D65" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="7"/>
+        <v>46202</v>
+      </c>
+      <c r="E65" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F65" s="6">
+        <v>262701686</v>
+      </c>
       <c r="G65" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>175</v>
+        <v>110</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="K65" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L65" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M65" s="3">
         <v>0</v>
       </c>
       <c r="N65" s="4">
-        <v>2121.5700000000002</v>
+        <v>2155.2600000000002</v>
       </c>
       <c r="O65" s="4">
-        <v>2121.5700000000002</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>163</v>
+        <v>23707.86</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>396</v>
+        <v>202</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>397</v>
+        <v>206</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D66" s="5">
-        <v>46216</v>
-      </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="7"/>
+        <v>46202</v>
+      </c>
+      <c r="E66" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F66" s="6">
+        <v>262701686</v>
+      </c>
       <c r="G66" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>182</v>
+        <v>90</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="K66" s="4">
         <v>2</v>
@@ -25322,198 +25078,210 @@
         <v>0</v>
       </c>
       <c r="N66" s="4">
-        <v>2541.7399999999998</v>
+        <v>10137.01</v>
       </c>
       <c r="O66" s="4">
-        <v>5083.4799999999996</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>163</v>
+        <v>20274.02</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>398</v>
+        <v>202</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>399</v>
+        <v>207</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D67" s="5">
-        <v>46213</v>
-      </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="7"/>
+        <v>46202</v>
+      </c>
+      <c r="E67" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F67" s="6">
+        <v>262701686</v>
+      </c>
       <c r="G67" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="I67" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>402</v>
+        <v>178</v>
       </c>
       <c r="K67" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L67" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M67" s="3">
         <v>0</v>
       </c>
       <c r="N67" s="4">
-        <v>5033.2</v>
+        <v>1548.9</v>
       </c>
       <c r="O67" s="4">
-        <v>5033.2</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>163</v>
+        <v>4646.7000000000007</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>398</v>
+        <v>202</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>403</v>
+        <v>208</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D68" s="5">
-        <v>46213</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="7"/>
+        <v>46202</v>
+      </c>
+      <c r="E68" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F68" s="6">
+        <v>262701686</v>
+      </c>
       <c r="G68" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="I68" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J68" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="J68" s="4" t="s">
-        <v>406</v>
-      </c>
       <c r="K68" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L68" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M68" s="3">
         <v>0</v>
       </c>
       <c r="N68" s="4">
-        <v>1074.28</v>
+        <v>10137.01</v>
       </c>
       <c r="O68" s="4">
-        <v>1074.28</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>163</v>
+        <v>40548.04</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>407</v>
+        <v>202</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>408</v>
+        <v>209</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D69" s="5">
-        <v>46213</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="7"/>
+        <v>46202</v>
+      </c>
+      <c r="E69" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F69" s="6">
+        <v>262701686</v>
+      </c>
       <c r="G69" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I69" s="7" t="s">
-        <v>176</v>
+        <v>116</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="K69" s="4">
         <v>9</v>
       </c>
       <c r="L69" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M69" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N69" s="4">
-        <v>4054.39</v>
+        <v>959.11</v>
       </c>
       <c r="O69" s="4">
-        <v>36489.51</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>163</v>
+        <v>8631.99</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B70" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="C70" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D70" s="5">
-        <v>46192</v>
-      </c>
-      <c r="E70" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F70" s="7">
-        <v>262701710</v>
+        <v>46202</v>
+      </c>
+      <c r="E70" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F70" s="6">
+        <v>262701686</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I70" s="7" t="s">
-        <v>181</v>
+        <v>102</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="K70" s="4">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="L70" s="4">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
       <c r="N70" s="4">
-        <v>5452.69</v>
+        <v>1461.23</v>
       </c>
       <c r="O70" s="4">
-        <v>245371.05</v>
+        <v>1461.23</v>
       </c>
       <c r="P70" s="4" t="s">
         <v>18</v>
@@ -25521,49 +25289,49 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D71" s="5">
-        <v>46192</v>
-      </c>
-      <c r="E71" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F71" s="7">
-        <v>262701710</v>
+        <v>46202</v>
+      </c>
+      <c r="E71" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F71" s="6">
+        <v>262701686</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="I71" s="7" t="s">
-        <v>182</v>
+        <v>172</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="K71" s="4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="L71" s="4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="M71" s="3">
         <v>0</v>
       </c>
       <c r="N71" s="4">
-        <v>5942</v>
+        <v>2541.7399999999998</v>
       </c>
       <c r="O71" s="4">
-        <v>166376</v>
+        <v>5083.4799999999996</v>
       </c>
       <c r="P71" s="4" t="s">
         <v>18</v>
@@ -25571,49 +25339,49 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D72" s="5">
-        <v>46192</v>
-      </c>
-      <c r="E72" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F72" s="7">
-        <v>262701710</v>
+        <v>46202</v>
+      </c>
+      <c r="E72" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F72" s="6">
+        <v>262701686</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="K72" s="4">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="L72" s="4">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
       </c>
       <c r="N72" s="4">
-        <v>5033.2</v>
+        <v>1524.79</v>
       </c>
       <c r="O72" s="4">
-        <v>427822</v>
+        <v>3049.58</v>
       </c>
       <c r="P72" s="4" t="s">
         <v>18</v>
@@ -25621,49 +25389,49 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D73" s="5">
-        <v>46192</v>
-      </c>
-      <c r="E73" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F73" s="7">
-        <v>262701710</v>
+        <v>46202</v>
+      </c>
+      <c r="E73" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F73" s="6">
+        <v>262701686</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>179</v>
+        <v>76</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="K73" s="4">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="M73" s="3">
         <v>0</v>
       </c>
       <c r="N73" s="4">
-        <v>3844.64</v>
+        <v>2020.51</v>
       </c>
       <c r="O73" s="4">
-        <v>742015.52</v>
+        <v>4041.02</v>
       </c>
       <c r="P73" s="4" t="s">
         <v>18</v>
@@ -25671,49 +25439,49 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>194</v>
+        <v>31</v>
       </c>
       <c r="D74" s="5">
-        <v>46193</v>
-      </c>
-      <c r="E74" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F74" s="7">
-        <v>262701495</v>
+        <v>46202</v>
+      </c>
+      <c r="E74" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F74" s="6">
+        <v>262701686</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>175</v>
+        <v>61</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="K74" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L74" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="9">
-        <v>8808.6228813559319</v>
-      </c>
-      <c r="O74" s="9">
-        <v>44043.114406779656</v>
+      <c r="N74" s="4">
+        <v>2935.74</v>
+      </c>
+      <c r="O74" s="4">
+        <v>2935.74</v>
       </c>
       <c r="P74" s="4" t="s">
         <v>18</v>
@@ -25721,49 +25489,49 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>194</v>
+        <v>31</v>
       </c>
       <c r="D75" s="5">
-        <v>46193</v>
-      </c>
-      <c r="E75" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F75" s="7">
-        <v>262701495</v>
+        <v>46202</v>
+      </c>
+      <c r="E75" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F75" s="6">
+        <v>262701687</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I75" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="K75" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L75" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="9">
-        <v>10137.012711864407</v>
-      </c>
-      <c r="O75" s="9">
-        <v>50685.063559322036</v>
+      <c r="N75" s="4">
+        <v>1906.14</v>
+      </c>
+      <c r="O75" s="4">
+        <v>7624.56</v>
       </c>
       <c r="P75" s="4" t="s">
         <v>18</v>
@@ -25771,49 +25539,49 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="D76" s="5">
-        <v>46193</v>
-      </c>
-      <c r="E76" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F76" s="7">
-        <v>262701495</v>
+        <v>46209</v>
+      </c>
+      <c r="E76" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F76" s="6">
+        <v>262701739</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="I76" s="7" t="s">
-        <v>175</v>
+        <v>64</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="K76" s="4">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L76" s="4">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="M76" s="3">
         <v>0</v>
       </c>
-      <c r="N76" s="9">
-        <v>3984.4703389830511</v>
-      </c>
-      <c r="O76" s="9">
-        <v>19922.351694915254</v>
+      <c r="N76" s="4">
+        <v>7340.4</v>
+      </c>
+      <c r="O76" s="4">
+        <v>190850.4</v>
       </c>
       <c r="P76" s="4" t="s">
         <v>18</v>
@@ -25821,49 +25589,49 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D77" s="5">
-        <v>46202</v>
-      </c>
-      <c r="E77" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F77" s="7">
-        <v>262701711</v>
+        <v>46209</v>
+      </c>
+      <c r="E77" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F77" s="6">
+        <v>262701739</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I77" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>52</v>
+        <v>171</v>
       </c>
       <c r="K77" s="4">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="L77" s="4">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="9">
-        <v>3844.64</v>
-      </c>
-      <c r="O77" s="9">
-        <v>380619.36</v>
+      <c r="N77" s="4">
+        <v>1906.14</v>
+      </c>
+      <c r="O77" s="4">
+        <v>3812.28</v>
       </c>
       <c r="P77" s="4" t="s">
         <v>18</v>
@@ -25871,49 +25639,49 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D78" s="5">
-        <v>46205</v>
-      </c>
-      <c r="E78" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F78" s="7">
-        <v>262701715</v>
+        <v>46209</v>
+      </c>
+      <c r="E78" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F78" s="6">
+        <v>262701740</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>185</v>
+        <v>58</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="K78" s="4">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="L78" s="4">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="M78" s="3">
         <v>0</v>
       </c>
       <c r="N78" s="4">
-        <v>1548.9</v>
+        <v>1119.06</v>
       </c>
       <c r="O78" s="4">
-        <v>77445</v>
+        <v>12309.66</v>
       </c>
       <c r="P78" s="4" t="s">
         <v>18</v>
@@ -25921,49 +25689,49 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>291</v>
+        <v>241</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D79" s="5">
-        <v>46205</v>
-      </c>
-      <c r="E79" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F79" s="7">
-        <v>262701715</v>
+        <v>46209</v>
+      </c>
+      <c r="E79" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F79" s="6">
+        <v>262701740</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>179</v>
+        <v>230</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>52</v>
+        <v>232</v>
       </c>
       <c r="K79" s="4">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="L79" s="4">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="M79" s="3">
         <v>0</v>
       </c>
       <c r="N79" s="4">
-        <v>3844.64</v>
+        <v>1397.6694915254238</v>
       </c>
       <c r="O79" s="4">
-        <v>1153392</v>
+        <v>9783.6864406779678</v>
       </c>
       <c r="P79" s="4" t="s">
         <v>18</v>
@@ -25971,49 +25739,49 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>292</v>
+        <v>242</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D80" s="5">
-        <v>46205</v>
-      </c>
-      <c r="E80" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F80" s="7">
-        <v>262701715</v>
+        <v>46209</v>
+      </c>
+      <c r="E80" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F80" s="6">
+        <v>262701740</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I80" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="K80" s="4">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="L80" s="4">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="M80" s="3">
         <v>0</v>
       </c>
       <c r="N80" s="4">
-        <v>466.53</v>
+        <v>571.4</v>
       </c>
       <c r="O80" s="4">
-        <v>139959</v>
+        <v>571.4</v>
       </c>
       <c r="P80" s="4" t="s">
         <v>18</v>
@@ -26021,49 +25789,49 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D81" s="5">
         <v>46209</v>
       </c>
-      <c r="E81" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F81" s="7">
-        <v>262701723</v>
+      <c r="E81" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F81" s="6">
+        <v>262701740</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>182</v>
+        <v>128</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>304</v>
+        <v>130</v>
       </c>
       <c r="K81" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L81" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M81" s="3">
         <v>0</v>
       </c>
       <c r="N81" s="4">
-        <v>2541.7399999999998</v>
+        <v>412.5</v>
       </c>
       <c r="O81" s="4">
-        <v>25417.399999999998</v>
+        <v>2475</v>
       </c>
       <c r="P81" s="4" t="s">
         <v>18</v>
@@ -26071,49 +25839,49 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>305</v>
+        <v>239</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>306</v>
+        <v>244</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D82" s="5">
         <v>46209</v>
       </c>
-      <c r="E82" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F82" s="7">
-        <v>262701720</v>
+      <c r="E82" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F82" s="6">
+        <v>262701740</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>181</v>
+        <v>96</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="K82" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L82" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M82" s="3">
         <v>0</v>
       </c>
       <c r="N82" s="4">
-        <v>5452.69</v>
+        <v>1715.47</v>
       </c>
       <c r="O82" s="4">
-        <v>43621.52</v>
+        <v>8577.35</v>
       </c>
       <c r="P82" s="4" t="s">
         <v>18</v>
@@ -26121,49 +25889,49 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>305</v>
+        <v>239</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D83" s="5">
         <v>46209</v>
       </c>
-      <c r="E83" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F83" s="7">
-        <v>262701720</v>
+      <c r="E83" s="9">
+        <v>46222</v>
+      </c>
+      <c r="F83" s="6">
+        <v>262701740</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="I83" s="7" t="s">
-        <v>183</v>
+        <v>233</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="K83" s="4">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L83" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M83" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N83" s="4">
-        <v>6851</v>
+        <v>1133.9000000000001</v>
       </c>
       <c r="O83" s="4">
-        <v>109616</v>
+        <v>5669.5</v>
       </c>
       <c r="P83" s="4" t="s">
         <v>18</v>
@@ -26171,49 +25939,49 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D84" s="5">
         <v>46209</v>
       </c>
-      <c r="E84" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F84" s="7">
-        <v>262701720</v>
+      <c r="E84" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F84" s="6">
+        <v>262701729</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>185</v>
+        <v>230</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>311</v>
+        <v>232</v>
       </c>
       <c r="K84" s="4">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L84" s="4">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M84" s="3">
         <v>0</v>
       </c>
       <c r="N84" s="4">
-        <v>959.11</v>
+        <v>1397.6694915254238</v>
       </c>
       <c r="O84" s="4">
-        <v>15345.76</v>
+        <v>4193.0084745762715</v>
       </c>
       <c r="P84" s="4" t="s">
         <v>18</v>
@@ -26221,49 +25989,49 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>312</v>
+        <v>253</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D85" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E85" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F85" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E85" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F85" s="6">
+        <v>262701850</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>180</v>
+        <v>67</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="K85" s="4">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="L85" s="4">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="M85" s="3">
         <v>0</v>
       </c>
       <c r="N85" s="4">
-        <v>1119.06</v>
+        <v>3304.45</v>
       </c>
       <c r="O85" s="4">
-        <v>52595.82</v>
+        <v>3304.45</v>
       </c>
       <c r="P85" s="4" t="s">
         <v>18</v>
@@ -26271,49 +26039,49 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>313</v>
+        <v>254</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D86" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E86" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F86" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E86" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F86" s="6">
+        <v>262701850</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>180</v>
+        <v>157</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="K86" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L86" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M86" s="3">
         <v>0</v>
       </c>
       <c r="N86" s="4">
-        <v>1548.9</v>
+        <v>1751.02</v>
       </c>
       <c r="O86" s="4">
-        <v>6195.6</v>
+        <v>1751.02</v>
       </c>
       <c r="P86" s="4" t="s">
         <v>18</v>
@@ -26321,49 +26089,49 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D87" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E87" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F87" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E87" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F87" s="6">
+        <v>262701850</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H87" s="6" t="s">
         <v>180</v>
       </c>
+      <c r="I87" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="J87" s="4" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="K87" s="4">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="L87" s="4">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="M87" s="3">
         <v>0</v>
       </c>
       <c r="N87" s="4">
-        <v>1481.53</v>
+        <v>571.4</v>
       </c>
       <c r="O87" s="4">
-        <v>188154.31</v>
+        <v>1142.8</v>
       </c>
       <c r="P87" s="4" t="s">
         <v>18</v>
@@ -26371,49 +26139,49 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>315</v>
+        <v>256</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D88" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E88" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F88" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E88" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F88" s="6">
+        <v>262701850</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="K88" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L88" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M88" s="3">
         <v>0</v>
       </c>
       <c r="N88" s="4">
-        <v>444.27966101694915</v>
+        <v>2541.7399999999998</v>
       </c>
       <c r="O88" s="4">
-        <v>1777.1186440677966</v>
+        <v>5083.4799999999996</v>
       </c>
       <c r="P88" s="4" t="s">
         <v>18</v>
@@ -26421,34 +26189,34 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D89" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E89" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F89" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E89" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F89" s="6">
+        <v>262701850</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="I89" s="7" t="s">
-        <v>175</v>
+        <v>131</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K89" s="4">
         <v>1</v>
@@ -26460,10 +26228,10 @@
         <v>0</v>
       </c>
       <c r="N89" s="4">
-        <v>2865.83</v>
+        <v>2668.86</v>
       </c>
       <c r="O89" s="4">
-        <v>2865.83</v>
+        <v>2668.86</v>
       </c>
       <c r="P89" s="4" t="s">
         <v>18</v>
@@ -26471,49 +26239,49 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>317</v>
+        <v>258</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D90" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E90" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F90" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E90" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F90" s="6">
+        <v>262701850</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>182</v>
+        <v>166</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="K90" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L90" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M90" s="3">
         <v>0</v>
       </c>
       <c r="N90" s="4">
-        <v>3304.45</v>
+        <v>1626.38</v>
       </c>
       <c r="O90" s="4">
-        <v>9913.3499999999985</v>
+        <v>1626.38</v>
       </c>
       <c r="P90" s="4" t="s">
         <v>18</v>
@@ -26521,49 +26289,49 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D91" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E91" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F91" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E91" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F91" s="6">
+        <v>262701850</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I91" s="7" t="s">
-        <v>178</v>
+        <v>122</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="K91" s="4">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L91" s="4">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="4">
-        <v>2656.08</v>
+        <v>2900.78</v>
       </c>
       <c r="O91" s="4">
-        <v>63745.919999999998</v>
+        <v>2900.78</v>
       </c>
       <c r="P91" s="4" t="s">
         <v>18</v>
@@ -26571,34 +26339,34 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D92" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E92" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F92" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E92" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F92" s="6">
+        <v>262701850</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="I92" s="7" t="s">
-        <v>175</v>
+        <v>25</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="K92" s="4">
         <v>1</v>
@@ -26610,10 +26378,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="4">
-        <v>2568.69</v>
+        <v>348.94</v>
       </c>
       <c r="O92" s="4">
-        <v>2568.69</v>
+        <v>348.94</v>
       </c>
       <c r="P92" s="4" t="s">
         <v>18</v>
@@ -26621,49 +26389,49 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>320</v>
+        <v>261</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D93" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E93" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F93" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E93" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F93" s="6">
+        <v>262701850</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="I93" s="7" t="s">
-        <v>174</v>
+        <v>105</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>323</v>
+        <v>107</v>
       </c>
       <c r="K93" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L93" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M93" s="3">
         <v>0</v>
       </c>
       <c r="N93" s="4">
-        <v>1397.6694915254238</v>
+        <v>2935.74</v>
       </c>
       <c r="O93" s="4">
-        <v>15374.364406779663</v>
+        <v>2935.74</v>
       </c>
       <c r="P93" s="4" t="s">
         <v>18</v>
@@ -26671,34 +26439,34 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D94" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E94" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F94" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E94" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F94" s="6">
+        <v>262701850</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I94" s="7" t="s">
-        <v>179</v>
+        <v>236</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="K94" s="4">
         <v>1</v>
@@ -26710,10 +26478,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="4">
-        <v>959.11</v>
+        <v>4683.62</v>
       </c>
       <c r="O94" s="4">
-        <v>959.11</v>
+        <v>4683.62</v>
       </c>
       <c r="P94" s="4" t="s">
         <v>18</v>
@@ -26721,34 +26489,34 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>305</v>
+        <v>252</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>325</v>
+        <v>263</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D95" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E95" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F95" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E95" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F95" s="6">
+        <v>262701850</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I95" s="7" t="s">
-        <v>181</v>
+        <v>264</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="K95" s="4">
         <v>1</v>
@@ -26760,10 +26528,10 @@
         <v>0</v>
       </c>
       <c r="N95" s="4">
-        <v>1023.09</v>
+        <v>1616.28</v>
       </c>
       <c r="O95" s="4">
-        <v>1023.09</v>
+        <v>1616.28</v>
       </c>
       <c r="P95" s="4" t="s">
         <v>18</v>
@@ -26771,49 +26539,49 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>326</v>
+        <v>271</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D96" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E96" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F96" s="7">
-        <v>262701720</v>
+        <v>46216</v>
+      </c>
+      <c r="E96" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F96" s="6">
+        <v>262701849</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>181</v>
+        <v>224</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="K96" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L96" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="4">
-        <v>1119.06</v>
+        <v>2541.7399999999998</v>
       </c>
       <c r="O96" s="4">
-        <v>6714.36</v>
+        <v>5083.4799999999996</v>
       </c>
       <c r="P96" s="4" t="s">
         <v>18</v>
@@ -26821,49 +26589,49 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D97" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E97" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F97" s="7">
-        <v>262701720</v>
+        <v>46213</v>
+      </c>
+      <c r="E97" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F97" s="6">
+        <v>262701851</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>183</v>
+        <v>274</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="K97" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L97" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M97" s="3">
         <v>0</v>
       </c>
       <c r="N97" s="4">
-        <v>2460.3200000000002</v>
+        <v>5033.2</v>
       </c>
       <c r="O97" s="4">
-        <v>19682.560000000001</v>
+        <v>5033.2</v>
       </c>
       <c r="P97" s="4" t="s">
         <v>18</v>
@@ -26871,1256 +26639,56 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D98" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E98" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F98" s="7">
-        <v>262701720</v>
+        <v>46213</v>
+      </c>
+      <c r="E98" s="9">
+        <v>46221</v>
+      </c>
+      <c r="F98" s="6">
+        <v>262701851</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="I98" s="7" t="s">
-        <v>175</v>
+        <v>278</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="K98" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L98" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M98" s="3">
         <v>0</v>
       </c>
       <c r="N98" s="4">
-        <v>571.4</v>
+        <v>1074.28</v>
       </c>
       <c r="O98" s="4">
-        <v>5142.5999999999995</v>
+        <v>1074.28</v>
       </c>
       <c r="P98" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D99" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E99" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F99" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J99" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="K99" s="4">
-        <v>14</v>
-      </c>
-      <c r="L99" s="4">
-        <v>14</v>
-      </c>
-      <c r="M99" s="3">
-        <v>0</v>
-      </c>
-      <c r="N99" s="4">
-        <v>412.5</v>
-      </c>
-      <c r="O99" s="4">
-        <v>5775</v>
-      </c>
-      <c r="P99" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D100" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E100" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F100" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="I100" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K100" s="4">
-        <v>18</v>
-      </c>
-      <c r="L100" s="4">
-        <v>18</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="4">
-        <v>1818.39</v>
-      </c>
-      <c r="O100" s="4">
-        <v>32731.02</v>
-      </c>
-      <c r="P100" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D101" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E101" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F101" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I101" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="K101" s="4">
-        <v>8</v>
-      </c>
-      <c r="L101" s="4">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="4">
-        <v>2541.7399999999998</v>
-      </c>
-      <c r="O101" s="4">
-        <v>20333.919999999998</v>
-      </c>
-      <c r="P101" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D102" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E102" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F102" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I102" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K102" s="4">
-        <v>13</v>
-      </c>
-      <c r="L102" s="4">
-        <v>13</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="4">
-        <v>2668.86</v>
-      </c>
-      <c r="O102" s="4">
-        <v>34695.18</v>
-      </c>
-      <c r="P102" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D103" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E103" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F103" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I103" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K103" s="4">
-        <v>2</v>
-      </c>
-      <c r="L103" s="4">
-        <v>2</v>
-      </c>
-      <c r="M103" s="3">
-        <v>0</v>
-      </c>
-      <c r="N103" s="4">
-        <v>1245.72</v>
-      </c>
-      <c r="O103" s="4">
-        <v>2491.44</v>
-      </c>
-      <c r="P103" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D104" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E104" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F104" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="I104" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="K104" s="4">
-        <v>1</v>
-      </c>
-      <c r="L104" s="4">
-        <v>1</v>
-      </c>
-      <c r="M104" s="3">
-        <v>0</v>
-      </c>
-      <c r="N104" s="4">
-        <v>2726</v>
-      </c>
-      <c r="O104" s="4">
-        <v>2726</v>
-      </c>
-      <c r="P104" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D105" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E105" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F105" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="K105" s="4">
-        <v>1</v>
-      </c>
-      <c r="L105" s="4">
-        <v>1</v>
-      </c>
-      <c r="M105" s="3">
-        <v>0</v>
-      </c>
-      <c r="N105" s="4">
-        <v>5236.6499999999996</v>
-      </c>
-      <c r="O105" s="4">
-        <v>5236.6499999999996</v>
-      </c>
-      <c r="P105" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D106" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E106" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F106" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I106" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J106" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K106" s="4">
-        <v>30</v>
-      </c>
-      <c r="L106" s="4">
-        <v>30</v>
-      </c>
-      <c r="M106" s="3">
-        <v>0</v>
-      </c>
-      <c r="N106" s="4">
-        <v>1481.53</v>
-      </c>
-      <c r="O106" s="4">
-        <v>44445.9</v>
-      </c>
-      <c r="P106" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D107" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E107" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F107" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="I107" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="K107" s="4">
-        <v>38</v>
-      </c>
-      <c r="L107" s="4">
-        <v>38</v>
-      </c>
-      <c r="M107" s="3">
-        <v>0</v>
-      </c>
-      <c r="N107" s="4">
-        <v>3704.81</v>
-      </c>
-      <c r="O107" s="4">
-        <v>140782.78</v>
-      </c>
-      <c r="P107" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D108" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E108" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F108" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="I108" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J108" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="K108" s="4">
-        <v>1</v>
-      </c>
-      <c r="L108" s="4">
-        <v>1</v>
-      </c>
-      <c r="M108" s="3">
-        <v>0</v>
-      </c>
-      <c r="N108" s="4">
-        <v>1818.39</v>
-      </c>
-      <c r="O108" s="4">
-        <v>1818.39</v>
-      </c>
-      <c r="P108" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D109" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E109" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F109" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H109" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I109" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K109" s="4">
-        <v>9</v>
-      </c>
-      <c r="L109" s="4">
-        <v>9</v>
-      </c>
-      <c r="M109" s="3">
-        <v>0</v>
-      </c>
-      <c r="N109" s="4">
-        <v>1751.02</v>
-      </c>
-      <c r="O109" s="4">
-        <v>15759.18</v>
-      </c>
-      <c r="P109" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D110" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E110" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F110" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H110" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I110" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="K110" s="4">
-        <v>3</v>
-      </c>
-      <c r="L110" s="4">
-        <v>3</v>
-      </c>
-      <c r="M110" s="3">
-        <v>0</v>
-      </c>
-      <c r="N110" s="4">
-        <v>2900.78</v>
-      </c>
-      <c r="O110" s="4">
-        <v>8702.34</v>
-      </c>
-      <c r="P110" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D111" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E111" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F111" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I111" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="J111" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K111" s="4">
-        <v>25</v>
-      </c>
-      <c r="L111" s="4">
-        <v>25</v>
-      </c>
-      <c r="M111" s="3">
-        <v>0</v>
-      </c>
-      <c r="N111" s="4">
-        <v>1715.47</v>
-      </c>
-      <c r="O111" s="4">
-        <v>42886.75</v>
-      </c>
-      <c r="P111" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D112" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E112" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F112" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H112" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I112" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="J112" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K112" s="4">
-        <v>6</v>
-      </c>
-      <c r="L112" s="4">
-        <v>6</v>
-      </c>
-      <c r="M112" s="3">
-        <v>0</v>
-      </c>
-      <c r="N112" s="4">
-        <v>348.94</v>
-      </c>
-      <c r="O112" s="4">
-        <v>2093.64</v>
-      </c>
-      <c r="P112" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D113" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E113" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F113" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="I113" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="J113" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="K113" s="4">
-        <v>5</v>
-      </c>
-      <c r="L113" s="4">
-        <v>5</v>
-      </c>
-      <c r="M113" s="3">
-        <v>0</v>
-      </c>
-      <c r="N113" s="4">
-        <v>1467.58</v>
-      </c>
-      <c r="O113" s="4">
-        <v>7337.9</v>
-      </c>
-      <c r="P113" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D114" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E114" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F114" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="I114" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="K114" s="4">
-        <v>5</v>
-      </c>
-      <c r="L114" s="4">
-        <v>5</v>
-      </c>
-      <c r="M114" s="3">
-        <v>0</v>
-      </c>
-      <c r="N114" s="4">
-        <v>1133.9000000000001</v>
-      </c>
-      <c r="O114" s="4">
-        <v>5669.5</v>
-      </c>
-      <c r="P114" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D115" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E115" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F115" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="I115" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="J115" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K115" s="4">
-        <v>3</v>
-      </c>
-      <c r="L115" s="4">
-        <v>3</v>
-      </c>
-      <c r="M115" s="3">
-        <v>0</v>
-      </c>
-      <c r="N115" s="4">
-        <v>2935.74</v>
-      </c>
-      <c r="O115" s="4">
-        <v>8807.2199999999993</v>
-      </c>
-      <c r="P115" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D116" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E116" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F116" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="I116" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J116" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="K116" s="4">
-        <v>1</v>
-      </c>
-      <c r="L116" s="4">
-        <v>1</v>
-      </c>
-      <c r="M116" s="3">
-        <v>0</v>
-      </c>
-      <c r="N116" s="4">
-        <v>1885.77</v>
-      </c>
-      <c r="O116" s="4">
-        <v>1885.77</v>
-      </c>
-      <c r="P116" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D117" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E117" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F117" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="H117" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="I117" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="K117" s="4">
-        <v>1</v>
-      </c>
-      <c r="L117" s="4">
-        <v>1</v>
-      </c>
-      <c r="M117" s="3">
-        <v>0</v>
-      </c>
-      <c r="N117" s="4">
-        <v>4683.62</v>
-      </c>
-      <c r="O117" s="4">
-        <v>4683.62</v>
-      </c>
-      <c r="P117" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D118" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E118" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F118" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I118" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="K118" s="4">
-        <v>2</v>
-      </c>
-      <c r="L118" s="4">
-        <v>2</v>
-      </c>
-      <c r="M118" s="3">
-        <v>0</v>
-      </c>
-      <c r="N118" s="4">
-        <v>2935.74</v>
-      </c>
-      <c r="O118" s="4">
-        <v>5871.48</v>
-      </c>
-      <c r="P118" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D119" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E119" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F119" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="J119" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="K119" s="4">
-        <v>1</v>
-      </c>
-      <c r="L119" s="4">
-        <v>1</v>
-      </c>
-      <c r="M119" s="3">
-        <v>0</v>
-      </c>
-      <c r="N119" s="4">
-        <v>1548.9</v>
-      </c>
-      <c r="O119" s="4">
-        <v>1548.9</v>
-      </c>
-      <c r="P119" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D120" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E120" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F120" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I120" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J120" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K120" s="4">
-        <v>232</v>
-      </c>
-      <c r="L120" s="4">
-        <v>232</v>
-      </c>
-      <c r="M120" s="3">
-        <v>0</v>
-      </c>
-      <c r="N120" s="4">
-        <v>1919.45</v>
-      </c>
-      <c r="O120" s="4">
-        <v>445312.4</v>
-      </c>
-      <c r="P120" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D121" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E121" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F121" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I121" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K121" s="4">
-        <v>4</v>
-      </c>
-      <c r="L121" s="4">
-        <v>4</v>
-      </c>
-      <c r="M121" s="3">
-        <v>0</v>
-      </c>
-      <c r="N121" s="4">
-        <v>1548.9</v>
-      </c>
-      <c r="O121" s="4">
-        <v>6195.6</v>
-      </c>
-      <c r="P121" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D122" s="5">
-        <v>46209</v>
-      </c>
-      <c r="E122" s="11">
-        <v>46215</v>
-      </c>
-      <c r="F122" s="7">
-        <v>262701720</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I122" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K122" s="4">
-        <v>28</v>
-      </c>
-      <c r="L122" s="4">
-        <v>28</v>
-      </c>
-      <c r="M122" s="3">
-        <v>0</v>
-      </c>
-      <c r="N122" s="4">
-        <v>1346.78</v>
-      </c>
-      <c r="O122" s="4">
-        <v>37709.839999999997</v>
-      </c>
-      <c r="P122" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B69">
+  <conditionalFormatting sqref="B2:B56">
     <cfRule type="duplicateValues" dxfId="1536" priority="1537"/>
     <cfRule type="duplicateValues" dxfId="1537" priority="1538"/>
     <cfRule type="duplicateValues" dxfId="1538" priority="1539"/>
@@ -28634,7 +27202,7 @@
     <cfRule type="duplicateValues" dxfId="2047" priority="2047"/>
     <cfRule type="duplicateValues" dxfId="1791" priority="2048"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:B69">
+  <conditionalFormatting sqref="B9:B56">
     <cfRule type="duplicateValues" dxfId="1024" priority="1025"/>
     <cfRule type="duplicateValues" dxfId="1534" priority="1026"/>
     <cfRule type="duplicateValues" dxfId="1533" priority="1027"/>
@@ -29148,7 +27716,7 @@
     <cfRule type="duplicateValues" dxfId="1026" priority="1535"/>
     <cfRule type="duplicateValues" dxfId="1025" priority="1536"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70:B122">
+  <conditionalFormatting sqref="B58:B98">
     <cfRule type="duplicateValues" dxfId="1023" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1022" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1021" priority="3"/>
